--- a/fixtures/sources/sbti/companies-2026-10-21.xlsx
+++ b/fixtures/sources/sbti/companies-2026-10-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="422">
   <si>
     <t>sbti_id</t>
   </si>
@@ -137,12 +137,23 @@
     <t>Company change</t>
   </si>
   <si>
+    <t>Adidas AG</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Textiles, Apparel, Footwear and Luxury Goods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: adidas AG commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: adidas AG commits to reduce absolute scope 1 and 2 GHG emissions 70% by 2030 from a 2022 base year*. adidas AG also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel- and energy-related activities, upstream and downstream transportation and distribution, business travel, end-of-life treatment of sold products and downstream leased assets 42% within the same timeframe*. 
+*The target boundary includes land-related emisisons and removals from bioenergy feedstocks.  Long-Term Targets: adidas AG commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from 2022 base year. adidas AG also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.*
+*The target boundary includes land-related emisisons and removals from bioenergy feedstocks.                </t>
+  </si>
+  <si>
     <t>ALDI Nord Group</t>
   </si>
   <si>
-    <t>Germany</t>
-  </si>
-  <si>
     <t>Food and Staples Retailing</t>
   </si>
   <si>
@@ -182,17 +193,17 @@
     <t>Expired commitment</t>
   </si>
   <si>
-    <t>Anhui Shinhoo Canned Motor Pump Co., Ltd.</t>
+    <t>ANHUI PROVINCE TATFOOK MECHANICAL ELECTRONIC TECHNOLOGY CO., LTD.</t>
   </si>
   <si>
     <t>China</t>
   </si>
   <si>
-    <t>Electrical Equipment and Machinery</t>
+    <t>Technology Hardware and Equipment</t>
   </si>
   <si>
     <t xml:space="preserve">Near-Term Targets:
-Anhui Shinhoo Canned Motor Pump Co., Ltd. commits to reduce absolute scope 1 and 2 GHG emissions 75.0% by 2036 from a 2024 base year. Anhui Shinhoo Canned Motor Pump Co., Ltd. also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, upstream transportation and distribution, waste generated in operations, business travel, employee commuting, use of sold products, and end-of-life treatment of sold products 35.0% within the same timeframe.</t>
+ANHUI PROVINCE TATFOOK MECHANICAL ELECTRONIC TECHNOLOGY CO., LTD. commits to reduce absolute scope 1 and 2 GHG emissions 63.0% by 2035 from a 2024 base year. ANHUI PROVINCE TATFOOK MECHANICAL ELECTRONIC TECHNOLOGY CO., LTD. also commits to reduce absolute scope 3 GHG emissions from purchased goods and services and processing of sold products 37.5% within the same timeframe.</t>
   </si>
   <si>
     <t>Arla Foods</t>
@@ -213,6 +224,30 @@
     <t>Near-Term Targets: Arla Foods commits to reduce absolute scope 1 and 2 GHG emissions 63% by 2030 from a 2015 base year.* Arla Foods also commits that 82.6% of its suppliers by emissions covering purchased goods and services, capital goods, upstream and downstream transportation and distribution, waste generated in operations, and investments, will have science-based targets by 2029.* *The target boundary includes land-related emissions and removals from bioenergy feedstocks.      Arla Foods commits to reduce absolute scope 3 FLAG GHG emissions 30.3% by 2030 from a 2020 base year*. Arla Foods also commits to no deforestation across its primary deforestation-linked commodities, with a target date of December 31, 2025. *The target includes FLAG emissions and removals.</t>
   </si>
   <si>
+    <t>Asda Group Limited</t>
+  </si>
+  <si>
+    <t>United Kingdom of Great Britain and Northern Ireland</t>
+  </si>
+  <si>
+    <t>BA1.5 member</t>
+  </si>
+  <si>
+    <t>ASML Holdings</t>
+  </si>
+  <si>
+    <t>NL0010273215</t>
+  </si>
+  <si>
+    <t>724500Y6DUVHQD6OXN27</t>
+  </si>
+  <si>
+    <t>Semiconductors and Semiconductors Equipment</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target: ASML commits to reach net-zero greenhouse gas emissions across the value chain by 2040. Near-Term Targets: ASML commits to reduce absolute scope 1 and 2 GHG emissions 75% by 2030 from a 2019 base year. ASML also commits to reduce scope 3 GHG emissions 55% per million EUR value added within the same timeframe.   Long-Term Targets: ASML commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2040 from a 2019 base year. ASML also commits to reduce scope 3 GHG emissions 97% per million EUR value added within the same timeframe.</t>
+  </si>
+  <si>
     <t>ASOS</t>
   </si>
   <si>
@@ -222,12 +257,6 @@
     <t>213800H8DBB8JSKDW630</t>
   </si>
   <si>
-    <t>United Kingdom of Great Britain and Northern Ireland</t>
-  </si>
-  <si>
-    <t>Textiles, Apparel, Footwear and Luxury Goods</t>
-  </si>
-  <si>
     <t>FY2050</t>
   </si>
   <si>
@@ -243,16 +272,13 @@
     <t>Air Freight Transportation and Logistics</t>
   </si>
   <si>
-    <t>BA1.5 member</t>
-  </si>
-  <si>
     <t>Target set at parent company level</t>
   </si>
   <si>
-    <t>Avenga</t>
-  </si>
-  <si>
-    <t>315700MKV13CUO0P0Q80</t>
+    <t>Avenga Limited</t>
+  </si>
+  <si>
+    <t>315700QIOWC2FRJZMC35</t>
   </si>
   <si>
     <t>Aviva PLC</t>
@@ -274,6 +300,36 @@
   </si>
   <si>
     <t>Banken Champignons Groep BV</t>
+  </si>
+  <si>
+    <t>Barry Callebaut</t>
+  </si>
+  <si>
+    <t>CH0009002962</t>
+  </si>
+  <si>
+    <t>213800Y5RWKLDPUTT265</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall net-zero target:
+Barry Callebaut AG commits to reach net-zero greenhouse gas emissions across the value chain by FY2050.
+Near-term targets:
+Energy &amp; Industry: Barry Callebaut AG commits to reduce absolute scope 1 and 2 GHG emissions 42% by FY2030 from a FY2022 base year.*
+Barry Callebaut AG also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, capital goods, fuel- and energy-
+related activities, upstream transportation and distribution, waste generated in operations, business travel, employee commuting and end-of-life treatment of sold products 25% within the same timeframe. *The target boundary includes land-related emissions and removals from bioenergy
+feedstocks.
+FLAG: Barry Callebaut AG commits to reduce absolute scope 3 FLAG GHG emissions 30.3% by FY2030 from a FY2022 base year.* Barry
+Callebaut AG commits to no deforestation across its primary deforestation-linked commodities, with a target date of December 31, 2025.
+*Target includes FLAG emissions and removals.
+Long-term targets:
+Energy &amp; Industry: Barry Callebaut AG commits to reduce absolute scope 1 and scope 2 GHG emissions 90% by FY2050 from a FY2022 base
+year.* Barry Callebaut AG also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe. *The target boundary includes
+land-related emissions and removals from bioenergy feedstocks.
+FLAG: Barry Callebaut also commits to reduce absolute scope 3 FLAG GHG emissions 72% by FY2050 from a FY2022 base year.*
+*Target includes FLAG emissions and removals.</t>
   </si>
   <si>
     <t>BREEDON GROUP plc</t>
@@ -297,26 +353,37 @@
 *The target boundary includes land-related emissions and removals from bioenergy feedstocks. Long-Term Targets: Breedon Group plc commits to reduce absolute gross scope 1, 2 and 3 GHG emissions 95% by 2050 from a 2022 base year.*  *The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
   </si>
   <si>
-    <t>CARTON CAPITAL</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>Containers and Packaging</t>
-  </si>
-  <si>
-    <t>CeramTec GmbH</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-Term Targets:
-CeramTec GmbH commits to reduce absolute scope 1 and 2 GHG emissions 47.0% by 2030 from a 2023 base year. CeramTec GmbH also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, capital goods, upstream transportation and distribution and waste generated in operations 25.0% within the same timeframe.</t>
+    <t>CARTIER</t>
+  </si>
+  <si>
+    <t>CA1467721082</t>
+  </si>
+  <si>
+    <t>529900UC5WFH8T7VID35</t>
+  </si>
+  <si>
+    <t>Cartier commits to reduce absolute scope 1, 2 and 3 GHG emissions 46% by 2030 from a 2019 base year. Cartier commits to increase annual sourcing of renewable electricity from 48% in 2019 to 100% by 2021. And commits to continue annually sourcing 100% renewable electricity through 2030.</t>
+  </si>
+  <si>
+    <t>Ceposa AG</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Ceposa AG commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2023 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Cisco Systems, Inc.</t>
+  </si>
+  <si>
+    <t>US17275R1023</t>
+  </si>
+  <si>
+    <t>549300LKFJ962MZ46593</t>
+  </si>
+  <si>
+    <t>FY2040</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target Cisco commits to reach net-zero greenhouse gas emissions across the value chain by FY2040 from a FY2019 base year. Near-Term Targets Cisco commits to reduce absolute scope 1 and 2 GHG emissions 90% by FY2030 from a FY2019 base year. Cisco commits to reduce absolute scope 3 GHG emissions from purchased goods and services, upstream transportation and distribution, and use of sold products 30% by FY2030 from a FY2019 base year. Long-Term Targets Cisco commits to reduce absolute scope 1, 2, and 3 GHG emissions 90% by FY2040 from a FY2019 base year.</t>
   </si>
   <si>
     <t>Coca-Cola Europacific Partners</t>
@@ -353,6 +420,12 @@
     <t>5493008KEVFYPMGTXO33</t>
   </si>
   <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
     <t>Well-below 2°C</t>
   </si>
   <si>
@@ -369,9 +442,6 @@
   </si>
   <si>
     <t>549300EFP3TNG7JGVE49</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
   </si>
   <si>
     <t xml:space="preserve">Overall net-zero target:
@@ -393,10 +463,25 @@
 *This target includes FLAG emissions and removals.</t>
   </si>
   <si>
-    <t>DAIEI SEISAKUSHO CO.,LTD.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). DAIEI SEISAKUSHO CO.,LTD. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>Croatian Post Inc. (HP - Hrvatska posta d.d.)</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Southern Europe</t>
+  </si>
+  <si>
+    <t>Near-Term Targets: HP-Hrvatska Pošta d.d. commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2023 base year. HP-Hrvatska Pošta d.d. also commits to reduce absolute scope 3 GHG emissions  from purchased goods and services, capital goods, upstream transportation and distribution and waste generated in operations 25% within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Daiei Co., Ltd. (Hyogo)</t>
+  </si>
+  <si>
+    <t>Electrical Equipment and Machinery</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Daiei Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
     <t>Danone</t>
@@ -420,129 +505,233 @@
 ** The target includes FLAG emissions and removals. </t>
   </si>
   <si>
-    <t>Dexus</t>
-  </si>
-  <si>
-    <t>AU000000DXS1</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Australia and New Zealand</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Australian real estate investment trust Dexus commits to reduce absolute scope 1 and 2 GHG emissions 70% and absolute scope 3 emissions 25% by 2030 from a 2018 base year.</t>
-  </si>
-  <si>
-    <t>Elia Group</t>
-  </si>
-  <si>
-    <t>BE0003822393</t>
-  </si>
-  <si>
-    <t>549300S1MP1NFDIKT460</t>
+    <t>Deutsche Telekom AG</t>
+  </si>
+  <si>
+    <t>DE0005557508</t>
+  </si>
+  <si>
+    <t>549300V9QSIG4WX4GJ96</t>
+  </si>
+  <si>
+    <t>Telecommunication Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall net-zero target:
+Deutsche Telekom AG commits to reach net-zero greenhouse gas emissions across the value chain by 2040.
+Near-term targets:
+Deutsche Telekom AG commits to reduce absolute scope 1 and 2 GHG emissions 94% by
+2030 from a 2020 base year. Deutsche Telekom AG also commits to reduce absolute scope 3 GHG emissions 47% within the same timeframe.
+Long-term targets:
+Deutsche Telekom AG commits to reduce absolute scope 1 and 2 GHG emissions 90% by
+2040 from a 2020 base year. Deutsche Telekom AG also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Dextra Group plc</t>
+  </si>
+  <si>
+    <t>Elevance Health</t>
+  </si>
+  <si>
+    <t>US0367521038</t>
+  </si>
+  <si>
+    <t>8MYN82XMYQH89CTMTH67</t>
+  </si>
+  <si>
+    <t>Healthcare Providers and Services, and Healthcare Technology</t>
+  </si>
+  <si>
+    <t>Elevance Health Inc. commits to reduce absolute scope 1 GHG emissions 46.2% by 2030 from a 2019 base year. Elevance Health Inc. also commits to continue active annual sourcing of 100% renewable electricity through 2030. Elevance Health Inc. further commits that 75% of its suppliers by spend, covering purchased goods and services, will have science-based targets by 2028.</t>
+  </si>
+  <si>
+    <t>Epimentis</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals, Biotechnology and Life Sciences</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Epimentis commits to maintain zero scope 1 emissions through 2030. Epimentis also commits to reduce absolute scope 2 GHG emissions 42% by 2030 from a 2021 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Ericsson Group</t>
+  </si>
+  <si>
+    <t>SE0000108656</t>
+  </si>
+  <si>
+    <t>549300W9JLPW15XIFM52</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target
+Ericsson commits to reach net-zero greenhouse gas emissions across the value chain by
+FY2040.
+Near-Term Targets
+Ericsson commits to reduce absolute scope 1, 2 and 3 GHG emissions 50% by FY2030 from
+a FY2020 base year. Within this target, Ericsson commits to reduce absolute scope 1 and 2
+GHG emissions 90.0% and absolute scope 3 GHG emissions 50.0% within the same
+timeframe.
+Long-Term Targets
+Ericsson commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by FY2040 from a
+FY2020 base year.</t>
+  </si>
+  <si>
+    <t>Essity AB</t>
+  </si>
+  <si>
+    <t>SE0009922164</t>
+  </si>
+  <si>
+    <t>549300G8E6YUVJ1DA153</t>
+  </si>
+  <si>
+    <t>Consumer Durables, Household and Personal Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Essity commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: Essity commits to reduce absolute scope 1 and 2 GHG emissions 35% by 2030 from a 2016 base year.*
+Essity also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, upstream transportation and distribution, waste generated in operations, and end-of-life treatment of sold products 35% within the same timeframe.*
+* The target boundary includes biogenic emissions and removals from bioenergy feedstocks. Long-Term Targets: Essity commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by 2050 from a 2016 base year*.
+*The target boundary includes biogenic emissions and removals from bioenergy feedstocks.</t>
+  </si>
+  <si>
+    <t>Euro Fresh Foods</t>
   </si>
   <si>
     <t>Belgium</t>
   </si>
   <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Euro Fresh Foods commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2023 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Fairphone B.V</t>
+  </si>
+  <si>
+    <t>724500CMLPSLXBZSUL67</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). FairPhone B.V commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions. FairPhone B.V commits to reach net-zero by 2045. As part of this, FairPhone B.V commits to reduce scope 1+2+3 emissions 90% by 2045 from a 2022 base year.</t>
+  </si>
+  <si>
+    <t>Fujitasyouten Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Solid Waste Management Utilities</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Fujitasyouten Co., Ltd. commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Gebrüder Weiss GmbH</t>
+  </si>
+  <si>
+    <t>529900LOW4SAET952388</t>
+  </si>
+  <si>
+    <t>Ground Transportation - Trucking Transportation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Gebrüder Weiss Gesellschaft m.b.H commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: Gebrüder Weiss Gesellschaft m.b.H commits to reduce absolute scope 1 and 2 GHG emissions 60% by 2034 from a 2023 base year.* Gebrüder Weiss Gesellschaft m.b.H also commits to reduce well-to-wheel absolute scope 3 GHG emissions from total heavy road freight covering upstream transportation and distribution 40% within the same timeframe. Gebrüder Weiss Gesellschaft m.b.H further commits to reduce absolute scope 3 GHG emissions from purchased goods and services, capital goods, fuel- and energy-related activities, waste generated in operations, business travel, and employee commuting 35% within the same timeframe.* Gebrüder Weiss Gesellschaft m.b.H finally commits that 80% of its suppliers by emissions covering remaining upstream transportation and distribution will have science-based targets by 2029.
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks."  Long-Term Targets: Gebrüder Weiss Gesellschaft m.b.H commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2023 base year.* Gebrüder Weiss Gesellschaft m.b.H also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.*
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks. </t>
+  </si>
+  <si>
+    <t>GOJO Industries</t>
+  </si>
+  <si>
+    <t>549300TPYO8GZ8MUHP57</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target: GOJO Industries, Inc. commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: GOJO Industries, Inc. commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2022 base year. GOJO Industries, Inc. also  commits to increase active annual sourcing of renewable electricity from 7% in 2022 to 100% by 2030. GOJO Industries, Inc. further commits to reduce scope 3 GHG emissions 51.6% per thousand cases shipped by 2030 from a 2022 base year.    Long-Term Targets: GOJO Industries, Inc. commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2022 base year. GOJO Industries, Inc. also commits to reduce scope 3 GHG emissions 97% per thousand cases shipped within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Groupe Public Ferroviaire (GPF) – SNCF</t>
+  </si>
+  <si>
+    <t>Ground Transportation - Railroads Transportation</t>
+  </si>
+  <si>
+    <t>2°C</t>
+  </si>
+  <si>
+    <t>Passenger and goods transportation company Groupe Public Ferroviaire (GPF) – SNCF commits to reduce absolute scope 1 and 2 GHG emissions 26% by 2030 from a 2017 base-year. Groupe Public Ferroviaire (GPF) – SNCF also commits to reduce absolute scope 3 GHG emissions from fuel and energy related activities 26% by 2030 from a 2017 base-year. SNCF Groupe commits that 70% of its suppliers by emissions will set science-based targets by 2024.</t>
+  </si>
+  <si>
+    <t>The targets covering greenhouse gas emissions from company operations (scopes 1 and 2) are consistent with reductions required to keep warming to 2°C</t>
+  </si>
+  <si>
+    <t>H&amp;M Group</t>
+  </si>
+  <si>
+    <t>SE0000106270</t>
+  </si>
+  <si>
+    <t>529900O5RR7R39FRDM42</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target H&amp;M Group commits to reach net-zero greenhouse emissions across the value chain by FY2040 from a FY2019 base year. Near-Term Targets H&amp;M Group commits to reduce absolute scope 1 and 2 GHG emissions 56% by FY2030 from a FY2019 base year*. H&amp;M Group also commits to increase annual sourcing of renewable electricity from 90.6% in FY2019 to 100% by FY2030. H&amp;M Group finally commits to reduce absolute scope 3 GHG emissions 56% by FY2030 from a FY2019 base year. *The target boundary includes biogenic land-related emissions and removals from bioenergy feedstocks. Long-Term Targets H&amp;M Group commits to reduce scope 1 and 2 GHG emissions 90% by FY2040 from a FY2019 base year*. H&amp;M Group also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe. *The target boundary includes biogenic land-related emissions and removals from bioenergy feedstocks.</t>
+  </si>
+  <si>
+    <t>HelloFresh SE</t>
+  </si>
+  <si>
+    <t>DE000A161408</t>
+  </si>
+  <si>
+    <t>391200ZAF4V6XD2M9G57</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise Company</t>
+  </si>
+  <si>
+    <t>US42824C1099</t>
+  </si>
+  <si>
+    <t>549300BX44RGX6ANDV88</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target Hewlett Packard Enterprise commits to reach net-zero greenhouse gas emissions across the value chain by FY2040 from a FY2020 base year. Near-Term Targets Hewlett Packard Enterprise commits to reduce absolute scope 1 and 2 GHG emissions 70% by FY2030 from a FY2020 base year. Hewlett Packard Enterprise also commits to reduce absolute scope 3 GHG emissions 42% within the same timeframe. Long-Term Targets Hewlett Packard Enterprise commits to reduce absolute scope 1 and 2 emissions 90% by FY2040 from a FY2020 base year. Hewlett Packard Enterprise also commits to reduce absolute scope 3 emissions 90% within the same time frame.</t>
+  </si>
+  <si>
+    <t>HORIEORIMONO Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Professional Services</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). HORIEORIMONO Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2021 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>US40434L1052</t>
+  </si>
+  <si>
+    <t>WHKXQACZ14C5XRO8LW03</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target: HP Inc. commits to reach net-zero greenhouse gas emissions across the value chain by FY2040. Near-Term Targets: HP Inc. commits to reduce absolute scope 1, 2 and 3 GHG emissions 50% by FY2030 from a FY2019 base year. Long-Term Targets: HP Inc. commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by FY2040 from a FY2019 base year.</t>
+  </si>
+  <si>
+    <t>Iberdrola SA</t>
+  </si>
+  <si>
+    <t>ES0144580Y14</t>
+  </si>
+  <si>
+    <t>5QK37QC7NWOJ8D7WVQ45</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
     <t>Electric Utilities and Independent Power Producers and Energy Traders (including Fossil, Alternative and Nuclear Energy)</t>
   </si>
   <si>
-    <t xml:space="preserve">Near-Term Targets:
-Elia Group commits to reduce absolute scope 1 and 2 GHG emissions 66.57% by 2035 from a 2024 base year. Elia Group also commits to reduce scope 3 GHG emissions from purchased goods and services and capital goods 66.33% per MVA of new transformer capacity within the same timeframe.</t>
-  </si>
-  <si>
-    <t>Epiworld International Co., Ltd.</t>
-  </si>
-  <si>
-    <t>Semiconductors and Semiconductors Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-Term Targets:
-Epiworld International Co., Ltd. commits to reduce absolute scope 1 and 2 GHG emissions 63.0% by 2035 from a 2024 base year. Epiworld International Co., Ltd. also commits to reduce scope 3 GHG emissions from fuel- and energy-related activities and processing of sold products 66.4% per square meter of sold epitaxial wafer within the same timeframe.</t>
-  </si>
-  <si>
-    <t>Euro Packaging UK Limited</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Euro Packaging UK Limited commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2020 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Fairphone B.V</t>
-  </si>
-  <si>
-    <t>724500CMLPSLXBZSUL67</t>
-  </si>
-  <si>
-    <t>Technology Hardware and Equipment</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). FairPhone B.V commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions. FairPhone B.V commits to reach net-zero by 2045. As part of this, FairPhone B.V commits to reduce scope 1+2+3 emissions 90% by 2045 from a 2022 base year.</t>
-  </si>
-  <si>
-    <t>FUJIWARA MECENAT KENSETSU</t>
-  </si>
-  <si>
-    <t>Construction and Engineering</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs).FUJIWARA MECENAT KENSETSU commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Geelen Counterflow</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Geelen Counterflow commits to reduce absolute scope 1 and scope 2 GHG emissions 50% by 2030 from a 2018 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Gold Circuit Electronics Ltd.</t>
-  </si>
-  <si>
-    <t>TW0002368008</t>
-  </si>
-  <si>
-    <t>Taiwan, Province of China</t>
-  </si>
-  <si>
-    <t>Near-Term Targets: Gold Circuit Electronics Ltd. commits to reduce absolute scope 1 and 2 GHG emissions 46.7% by FY2030 from a FY2019 base year. Gold Circuit Electronics Ltd. also commits to reduce absolute scope 3 GHG emissions from purchased goods and services 25.0% by FY2030 from a FY2023 base year.</t>
-  </si>
-  <si>
-    <t>Groupe Rosa Holding</t>
-  </si>
-  <si>
-    <t>ROSA HOLDING commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2022 base year.  ROSA HOLDING also commits to increase active annual sourcing of renewable electricity from 68% in 2022 to 100% by 2030. ROSA HOLDING further commits to reduce scope 3 GHG emissions 51.6% per million EUR value added by 2030 from a 2022 base year.</t>
-  </si>
-  <si>
-    <t>H&amp;M Group</t>
-  </si>
-  <si>
-    <t>SE0000106270</t>
-  </si>
-  <si>
-    <t>529900O5RR7R39FRDM42</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>FY2040</t>
-  </si>
-  <si>
-    <t>Overall Net-Zero Target H&amp;M Group commits to reach net-zero greenhouse emissions across the value chain by FY2040 from a FY2019 base year. Near-Term Targets H&amp;M Group commits to reduce absolute scope 1 and 2 GHG emissions 56% by FY2030 from a FY2019 base year*. H&amp;M Group also commits to increase annual sourcing of renewable electricity from 90.6% in FY2019 to 100% by FY2030. H&amp;M Group finally commits to reduce absolute scope 3 GHG emissions 56% by FY2030 from a FY2019 base year. *The target boundary includes biogenic land-related emissions and removals from bioenergy feedstocks. Long-Term Targets H&amp;M Group commits to reduce scope 1 and 2 GHG emissions 90% by FY2040 from a FY2019 base year*. H&amp;M Group also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe. *The target boundary includes biogenic land-related emissions and removals from bioenergy feedstocks.</t>
-  </si>
-  <si>
-    <t>HORIZONTE Projects GmbH</t>
-  </si>
-  <si>
-    <t>Consumer Durables, Household and Personal Products</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Horizonte Textil GmbH commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by 2030 from a 2024 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>Overall Net-Zero Target Iberdrola SA commits to reach net-zero greenhouse gas emissions across the value chain by 2039 from a 2020 base year. Near-Term Targets Iberdrola SA commits to reduce absolute scope 1, 2 and 3 GHG emissions 65% by 2030 from a 2020 base year. Within that target, Iberdrola SA commits to reduce scope 1 and 2 GHG emissions from power generation 83% per kWh by 2030 from a 2020 base year. Iberdrola SA also commits to reduce scope 1 and 3 GHG emissions from fuel and energy related activities covering all sold electricity 85% per kWh within the same timeframe. Iberdrola SA further commits to reduce absolute scope 3 GHG emissions from use of sold products 42% within the same timeframe. Iberdrola SA finally commits to reduce all remaining absolute scope 3 GHG emissions 46% within the same timeframe. Long-Term Targets Iberdrola commits to reduce scope 1, 2 and 3 emissions 90% by 2039 from a 2020 base year. Within that target, Iberdrola SA commits to reduce scope 1 and 2 GHG emissions from power generation 84% per kWh by 2039 from a 2020 base year. Iberdrola SA also commits to reduce scope 1 and 3 GHG emissions from fuel and energy related activities covering all sold electricity 95% per kWh within the same timeframe. Iberdrola SA further commits to reduce absolute scope 3 GHG emissions from use of sold products 90% within the same timeframe. Iberdrola SA finally commits to reduce all remaining absolute scope 3 GHG emissions 90% within the same timeframe.</t>
   </si>
   <si>
     <t>IKEA</t>
@@ -557,10 +746,25 @@
 *The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
   </si>
   <si>
-    <t>Indica Labs, LLC</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Indica Labs, LLC commits to maintain zero scope 1 emissions through 2035. Indica Labs, LLC also commits to reduce absolute scope 2 GHG emissions 63% by 2035 from a 2025 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>INDEGENE LIMITED</t>
+  </si>
+  <si>
+    <t>INE065X01017</t>
+  </si>
+  <si>
+    <t>335800XFEREFIW9LG995</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Southern Asia</t>
+  </si>
+  <si>
+    <t>FY2028</t>
+  </si>
+  <si>
+    <t>Indegene Limited commits to reduce absolute scope 1 and 2 GHG emissions 33.6% by FY2028 from a FY2023 base year. Indegene Limited also commits to reduce absolute scope 3 GHG emissions 20.0% within the same timeframe.</t>
   </si>
   <si>
     <t>Inditex</t>
@@ -570,12 +774,6 @@
   </si>
   <si>
     <t>549300TTCXZOGZM2EY83</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Southern Europe</t>
   </si>
   <si>
     <t xml:space="preserve">Overall Net-Zero Target: Inditex commits to reach net-zero greenhouse gas emissions across the value chain by FY2040. Near-Term Targets: Inditex commits to reduce absolute scope 1, 2, and 3 GHG emissions 53% by FY2030 from a FY2018 base year. 
@@ -597,109 +795,141 @@
  *The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
   </si>
   <si>
-    <t>ITR Concession Company LLC</t>
-  </si>
-  <si>
-    <t>5493007GBY3OBTILCX44</t>
-  </si>
-  <si>
-    <t>Ground Transportation - Highways and Railtracks</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). ITR Concession Company LLC commits to reduce absolute scope 1 and scope 2 GHG emissions 50% by 2030 from a 2018 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>J Barbour &amp; Sons Ltd</t>
-  </si>
-  <si>
-    <t>FY2032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Net-Zero Target
-Barbour commits to reach net-zero greenhouse gas emissions across the value chain by
-FY2050.
-Near-Term Targets
-Barbour commits to reduce absolute scope 1 and 2 GHG emissions 60% by FY2032 from a
-FY2022 base year. Barbour commits to reduce absolute scope 3 GHG emissions from
-purchased goods and services, upstream transportation and distribution and downstream
-transportation and distribution 30% within the same timeframe.
-Long-Term Targets
-Barbour commits to reduce absolute scope 1 and 2 GHG emissions 90% by FY2050 from a
-FY2022 base year. Barbour commits to reduce absolute scope 3 GHG emissions from
-purchased goods and services, upstream transportation and distribution and downstream
-transportation and distribution 90% within the same timeframe.</t>
-  </si>
-  <si>
-    <t>JAWANDSONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>INE28UQ01014</t>
-  </si>
-  <si>
-    <t>984500E154EA5CRCDF77</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Southern Asia</t>
-  </si>
-  <si>
-    <t>FY2035</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). JAWANDSONS PRIVATE LIMITED commits to reduce absolute scope 1 and scope 2 GHG emissions 63% by FY2035 from a FY2024 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Joint Road Service Co., Ltd.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Joint Road Service Co., Ltd. commits to reduce absolute scope 1 and scope 2 GHG emissions 58.8% by 2034 from a 2024 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Kamstrup A/S</t>
-  </si>
-  <si>
-    <t>Overall Net-Zero Target: Kamstrup commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: Kamstrup commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2023 base year. Kamstrup also commits to reduce absolute scope 3 GHG emissions 42% within the same timeframe.  Long-Term Targets: Kamstrup commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2023 base year. Kamstrup also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.</t>
-  </si>
-  <si>
-    <t>Kisyou Co., Ltd.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Kisyou Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2020 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>KOVERLUX SRL</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). KOVERLUX SRL commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2021 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>KT Co., Ltd.</t>
-  </si>
-  <si>
-    <t>Ground Transportation - Trucking Transportation</t>
-  </si>
-  <si>
-    <t>FY2034</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). KT Co., Ltd. commits to reduce absolute scope 1 and scope 2 GHG emissions 58.8% by FY2034 from a FY2024 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>KUNIKEN. Co., Ltd.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). KUNIKEN. Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 46% by 2030 from a 2019 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>LOTTE CO., LTD.</t>
-  </si>
-  <si>
-    <t>LOTTE CO. , LTD. commits to reduce absolute scope 1 and 2 GHG emissions 23% by 2028 from a 2019 base year. LOTTE CO. , LTD. also commits to reduce absolute scope 3 GHG emissions from fuel and energy related activities 23% within the same timeframe. LOTTE CO. , LTD. also commits that 80% of its suppliers by emissions covering purchased goods and services, capital goods, and upstream transportation and distribution will have SBTs by 2027</t>
+    <t>innocent drinks</t>
+  </si>
+  <si>
+    <t>ITOKOGYO Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). ITOKOGYO　Co.,Ltd. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>İHLAS GAZETECİLİK A.Ş.</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Western Asia</t>
+  </si>
+  <si>
+    <t>Forest and Paper Products - Forestry, Timber, Pulp and Paper, Rubber</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). İHLAS GAZETECİLİK A.Ş. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>JAS-FBG S.A.</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Eastern Europe</t>
+  </si>
+  <si>
+    <t>JBS</t>
+  </si>
+  <si>
+    <t>BRJBSSACNOR8</t>
+  </si>
+  <si>
+    <t>529900RM0MTMZL9O5050</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Johnson Matthey Plc</t>
+  </si>
+  <si>
+    <t>GB00BZ4BQC70</t>
+  </si>
+  <si>
+    <t>2138001AVBSD1HSC6Z10</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Johnson Matthey Plc commits to reach net-zero greenhouse gas emissions across the value chain by FY2040.
+Near-Term Targets: Johnson Matthey commits to reduce absolute scope 1 and 2 GHG emissions 44% by FY2030 from a FY2020 base year. Johnson Matthey also commits to reduce absolute scope 3 GHG emissions from purchased goods and services 42% within the same timeframe.
+Long-Term Targets: Johnson Matthey commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by FY2040 from a FY2020 base year.</t>
+  </si>
+  <si>
+    <t>Kampsen GmbH &amp; Co KG</t>
+  </si>
+  <si>
+    <t>Kingfisher plc</t>
+  </si>
+  <si>
+    <t>GB0033195214</t>
+  </si>
+  <si>
+    <t>213800KBMEV7I92FY281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target:
+Kingfisher plc commits to achieve net-zero greenhouse gas emissions across the value chain by FY2050.
+Near-Term Targets:
+Kingfisher plc commits to reduce absolute scope 1 and 2 GHG emissions 70.23% by FY2030 from a FY2017 base year. * Kingfisher plc also commits to reduce absolute scope 3 GHG emissions from purchased goods and services and use of sold products 46.0% within the same timeframe. Kingfisher plc further commits to reduce absolute scope 3 GHG emissions from use of sold products for sold fossil fuels 54.61% within the same timeframe.
+Long-Term Targets:
+Kingfisher plc commits to reduce absolute scope 1 and 2 GHG emissions 90.0% by FY2040 from a FY2017 base year. * Kingfisher plc also commits to reduce absolute scope 3 GHG emissions from purchased goods and services and use of sold products 90.0% by FY2050 from a FY2017 base year. Kingfisher plc further commits to reduce absolute scope 3 GHG emissions from use of sold products for sold fossil fuels 90.0% within the same timeframe.
+*The target boundary includes land-related emissions and removals from biogenic feedstocks.</t>
+  </si>
+  <si>
+    <t>KISOGAWASENJYU CO.,LTD.</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). KISOGAWASENJYU CO.,LTD. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>KOUWA-TEC CO.,LTD</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). KOUWA-TEC CO.,LTD commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>KSG Catering</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Kunert Wellpappe</t>
+  </si>
+  <si>
+    <t>Containers and Packaging</t>
+  </si>
+  <si>
+    <t>Legrand</t>
+  </si>
+  <si>
+    <t>FR0010307819</t>
+  </si>
+  <si>
+    <t>969500XXRPGD7HCAFA90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Legrand commits to reach net-zero greenhouse gas emissions
+across the value chain by 2050.
+Near-Term Targets: Legrand commits to reduce absolute scope 1 and 2 GHG emissions 42%
+by 2030 from a 2022 base year.
+Legrand commits to reduce absolute scope 3 GHG emissions from purchased goods and
+services and use of sold products 25% within the same timeframe.
+Long-Term Targets: Legrand commits to reduce absolute scope 1 and 2 GHG emissions 90%
+by 2050 from a 2022 base year.
+Legrand commits to reduce absolute scope 3 GHG emissions 90% within the same
+timeframe.</t>
+  </si>
+  <si>
+    <t>Lothar Medtec GmbH</t>
+  </si>
+  <si>
+    <t>Healthcare Equipment and Supplies</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Lothar Medtec GmbH commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2023 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
     <t>Mammut Sports Group</t>
@@ -717,22 +947,75 @@
 Mammut Sports Group AG commits to reduce absolute scope 1, 2, and 3 GHG emissions 90% by 2050 from a 2018 base year.</t>
   </si>
   <si>
-    <t>Milchwerke Ingolstadt - Thalmaessing eG</t>
-  </si>
-  <si>
-    <t>MINE SYOTEN CO.,LTD.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). MINE SYOTEN CO.,LTD. commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Monaghan Mushrooms</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Food Production - Agricultural Production</t>
+    <t>Mango Punto Fa, SL</t>
+  </si>
+  <si>
+    <t>Mango commits to reduce absolute scope 1 and 2 GHG emissions 80% by 2030 from a 2019 base year. Mango also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel and energy related activities, and upstream transport and distribution 35% within the same timeframe</t>
+  </si>
+  <si>
+    <t>McDonald's Corporation</t>
+  </si>
+  <si>
+    <t>US5801351017</t>
+  </si>
+  <si>
+    <t>UE2136O97NLB5BYP9H04</t>
+  </si>
+  <si>
+    <t>Hotels, Restaurants and Leisure, and Tourism Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target
+McDonald’s Corporation commits to reach net-zero GHG emissions across the value chain
+by 2050.
+Near-Term Targets
+Energy and industrial: McDonald’s Corporation commits to reduce absolute scope 1 and 2
+GHG emissions 50.4% by 2030 from a 2018 base year. McDonald’s Corporation also commits
+to reduce absolute scope 3 energy and industrial GHG emissions from purchased goods and
+services, fuel and energy related activities, upstream transportation and distribution, waste
+generated in operations, end-of-life treatment of sold products, and franchises 50.4% within
+the same timeframe.
+FLAG: McDonald’s Corporation commits to reduce absolute scope 3 FLAG GHG emissions 16%
+by 2030 from a 2018 base year.* McDonald’s Corporation also commits to maintain no
+deforestation across its primary deforestation-linked commodities.
+Long-Term Targets
+Energy and industrial: McDonald’s Corporation commits to reduce absolute scope 1, 2, and
+energy and industrial scope 3 GHG emissions 90% by 2050 from a 2018 base year.
+FLAG: McDonald’s Corporation also commits to reduce absolute scope 3 GHG emissions 72%
+by 2050 from a 2018 base year.*
+*Target includes FLAG emissions and removals.</t>
+  </si>
+  <si>
+    <t>Milarex AS</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy &amp; Industry:
+Milarex AS commits to reduce absolute scope 1 and 2 GHG emissions 50.4% by 2032 from a 2022 base year.* Milarex AS also commits that 79% of its suppliers by emissions covering
+purchased goods and services, will have science-based targets by 2028.
+*The target boundary includes land-related emissions and removals from bioenergy
+feedstocks.
+FLAG:
+Milarex AS commits to reduce absolute scope 3 FLAG GHG emissions 36.4% by 2032 from a 2022 base year.** Milarex AS commits to no deforestation across its primary deforestation-
+linked commodities, with a target date of December 31, 2025.
+**The target includes FLAG emissions and removals.</t>
+  </si>
+  <si>
+    <t>MINDSNOB CONSULTING PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). MINDSNOB CONSULTING PRIVATE LIMITED commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions. MINDSNOB CONSULTING PRIVATE LIMITED commits to reach net-zero by 2035. As part of this, MINDSNOB CONSULTING PRIVATE LIMITED commits to reduce scope 1+2+3 emissions 90% by 2035 from a 2022 base year.</t>
+  </si>
+  <si>
+    <t>Momo Line srl</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs).Momo Line srl commits to reduce absolute scope 1 and scope 2 GHG emissions 38% by 2029 from a 2023 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
     <t>Nestlé</t>
@@ -778,24 +1061,84 @@
 **The target includes FLAG emissions and removals.</t>
   </si>
   <si>
-    <t>NetONE Network Solution Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>Thailand</t>
-  </si>
-  <si>
-    <t>South-eastern Asia</t>
+    <t>netgo group GmbH</t>
+  </si>
+  <si>
+    <t>529900ZKSU8FMB3ISH89</t>
+  </si>
+  <si>
+    <t>NIKE, Inc.</t>
+  </si>
+  <si>
+    <t>US6541061031</t>
+  </si>
+  <si>
+    <t>787RXPR0UX0O0XUXPZ81</t>
   </si>
   <si>
     <t xml:space="preserve">Near-Term Targets:
-NetONE Network Solution Co.,Ltd. commits to reduce absolute scope scope 1, 2 and 3 GHG emissions 44.51% by 2030 from a 2024 base year. Within this target, NetONE Network Solution Co.,Ltd. commits to reduce absolute scope 1 and 2 GHG emissions 42.3% by 2030 from a 2024 base year and scope 3 GHG emissions from purchased goods and services, capital goods, fuel- and energy-related activities, upstream transportation and distribution, waste generated in operations, business travel, employee commuting, downstream transportation and distribution, use of sold products, end-of-life treatment of sold products and downstream leased assets 55.3% per unit sold within the same timeframe.</t>
-  </si>
-  <si>
-    <t>NOBLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-Term Targets:
-NOBLE commits to reduce absolute scope 1 and 2 GHG emissions 55.0% by FY2030 from a FY2024 base year. NOBLE also commits to reduce absolute scope 3 GHG emissions 25.0% within the same timeframe.</t>
+NIKE, Inc. commits to reduce absolute scope 1 and 2 GHG emissions 75.5% by FY2030 from a FY2020 base year.* NIKE, Inc. also commits to reduce absolute scope 3 GHG emissions 35.0% within the same timeframe.
+*The target boundary includes land-related emissions and removals from biogenic feedstocks.</t>
+  </si>
+  <si>
+    <t>Nobia AB</t>
+  </si>
+  <si>
+    <t>SE0000949331</t>
+  </si>
+  <si>
+    <t>529900MZ8Y3QGPDF6815</t>
+  </si>
+  <si>
+    <t>Nobia AB commits to reduce absolute scope 1 and 2 GHG emissions 72% by 2026 from a 2016 base year*. Nobia AB also commits that 70% of its suppliers by emissions covering purchased goods and services and use of sold products, will have science-based targets by 2025. *The target boundary includes biogenic emissions and removals from bioenergy feedstocks.</t>
+  </si>
+  <si>
+    <t>Nokia Group</t>
+  </si>
+  <si>
+    <t>FI0009000681</t>
+  </si>
+  <si>
+    <t>549300A0JPRWG1KI7U06</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Nokia commits to reach net-zero greenhouse gas emissions across the value chain by 2040. Near-Term Targets: Nokia commits to reduce absolute scope 1, 2 and 3 GHG emissions 50% by 2030 from a 2019 base year.  Long-Term Targets: Nokia commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by 2040 from a 2019 base year.  </t>
+  </si>
+  <si>
+    <t>Novo Nordisk A/S</t>
+  </si>
+  <si>
+    <t>DK0060534915</t>
+  </si>
+  <si>
+    <t>549300DAQ1CVT6CXN342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: 
+Novo Nordisk A/S commits to reach net-zero greenhouse gas emissions across the value chain by 2045.
+Near-Term Targets: 
+Novo Nordisk A/S commits to reduce absolute scope 1 and 2 GHG emissions 100% by 2030 from a 2024 base year.* Novo Nordisk A/S also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, capital goods, upstream transportation and distribution, business travel, and downstream transportation and distribution 33% by 2033 from a 2024 base year.
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.
+Long-Term Targets: 
+Novo Nordisk commits to maintain a minimum of 100% absolute scope 1 and 2 GHG emissions reduction from 2030 through 2045 from a 2024 base year.* Novo Nordisk A/S also commits to reduce absolute scope 3 GHG emissions 90% by 2045 from a 2024 base year.*
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
+  </si>
+  <si>
+    <t>Novozymes A/S (part of the Novonesis group)</t>
+  </si>
+  <si>
+    <t>DK0060336014</t>
+  </si>
+  <si>
+    <t>529900T6WNZXD2R3JW38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target Novozymes A/S commits to reach net zero GHG emissions across the value chain by 2050 from a 2018 base year.
+Near-Term Targets Novozymes A/S commits to reduce absolute scope 1 and 2 GHG emissions 75% by 2030 from a 2018 base year*. Novozymes A/S also commits to increase annual sourcing of renewable electricity from 37% in 2018 to 100% by 2025 and maintain 100% sourcing of renewable electricity through 2030. Novozymes A/S further commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel and energy related activities, upstream transportation and distribution, waste generated in operations and business travel 35% by 2030 from a 2018 base year. *The target boundary includes biogenic emissions and removals associated with the use of bioenergy. 
+Long-Term Targets Novozymes A/S commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2018 base year*. Novozymes A/S also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel and energy related activities, upstream transportation and distribution, waste generated in operations and business travel 90% within the same timeframe. *The target boundary includes biogenic emissions and removals associated with the use of bioenergy.</t>
   </si>
   <si>
     <t>Oesterreichische Post AG (Austrian Post)</t>
@@ -821,46 +1164,79 @@
     <t>Overall Net-Zero Target Patagonia Works commits to reach net-zero greenhouse gas emissions across the value chain by FY2040 from a FY2017 base year. Near-Term Targets Patagonia Works commits to reduce absolute scope 1 and 2 GHG emissions 80% by FY2030 from a FY2017 base year. Patagonia Works also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, upstream transportation and distribution, business travel, and downstream transportation and distribution 55% within the same timeframe. Long-Term Targets Patagonia Works commits to reduce absolute scope 1, 2, and 3 GHG emissions 90% by FY2040 from a FY2017 base year.</t>
   </si>
   <si>
-    <t>Permanent Planet Corporation</t>
-  </si>
-  <si>
-    <t>Professional Services</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs).Permanent Planet Corporation commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>PharmaBlock Sciences (Nanjing), Inc.</t>
-  </si>
-  <si>
-    <t>CNE1000035K5</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals, Biotechnology and Life Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-Term Targets:
-PharmaBlock Sciences (Nanjing), Inc. commits to reduce absolute scope 1 and 2 GHG emissions 63.0% by 2035 from a 2024 base year. PharmaBlock Sciences (Nanjing), Inc. also commits to reduce scope 3 GHG emissions 66.33% per CNY value added within the same timeframe.</t>
-  </si>
-  <si>
-    <t>PROMO EVENTS, d. o. o</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Specialized Consumer Services</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). PROMO EVENTS, d. o. o commits to maintain zero scope 1 emissions through 2030. PROMO EVENTS, d. o. o also commits to reduce absolute scope 2 GHG emissions 42% by 2030 from a 2024 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>PepsiCo, Inc.</t>
+  </si>
+  <si>
+    <t>US7134481081</t>
+  </si>
+  <si>
+    <t>FJSUNZKFNQ5YPJ5OT455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall net-zero target:
+PepsiCo, Inc. commits to reach net-zero greenhouse gas emissions across the value chain by 2050.
+Near-term targets:
+Energy &amp; Industry: PepsiCo, Inc. commits to reduce absolute scope 1 and 2 GHG emissions 50% by 2030 from a 2022 base year.* PepsiCo,
+Inc. also commits to reduce absolute scope 3 GHG emissions rom purchased goods and services, fuel and energy related activities, business
+travel, downstream transportation and distribution and franchises 42% within the same timeframe.
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.
+FLAG: PepsiCo, Inc. commits to reduce absolute scope 3 FLAG GHG emissions 30.3% by 2030 from a 2022 base year.** PepsiCo, Inc. also
+commits to no deforestation across its primary deforestation-linked commodities, with a target date of December 31, 2025.
+**The target includes FLAG emissions and removals.
+Long-term targets:
+Energy &amp; Industry: PepsiCo, Inc. commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2022 base year.* PepsiCo,
+Inc. also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.
+FLAG: PepsiCo, Inc. commits to reduce absolute scope 3 FLAG GHG emissions 72% by 2050 from a 2022 base year.**
+**The target includes FLAG emissions and removals.</t>
+  </si>
+  <si>
+    <t>Perlen Packaging</t>
+  </si>
+  <si>
+    <t>PharmaACE LLC (Group)</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). PharmaACE LLC (Group) commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Primark Limited</t>
+  </si>
+  <si>
+    <t>21380028ZBNXSR21LL96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primark commits to reduce absolute scope 1 and 2 GHG emissions 50% by
+2030 from a 2019 base year. Primark also commits to reduce absolute
+scope 3 GHG emissions from purchased goods and services 50% within the
+same timeframe.</t>
+  </si>
+  <si>
+    <t>Promicron AG</t>
+  </si>
+  <si>
+    <t>529900ARYHFO3LPPHA90</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Promicron AG commits to reduce absolute scope 1 and scope 2 GHG emissions 58.8% by 2034 from a 2024 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>PUMA SE</t>
+  </si>
+  <si>
+    <t>DE0006969603</t>
+  </si>
+  <si>
+    <t>529900GRZ2BQY5ZM9N49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUMA commits to reduce absolute scope 1 and scope 2 GHG emissions 90% by 2030 from a 2017 base year. PUMA SE also commits to continue active annual sourcing of 100% renewable electricity through 2030. PUMA further commits to reduce absolute scope 3 GHG emissions from purchased goods and services and upstream transportation and distribution 33% by 2030 from a 2017 base year.*
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
   </si>
   <si>
     <t>Recover Group</t>
   </si>
   <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Trading Companies and Distributors, and Commercial Services and Supplies</t>
   </si>
   <si>
@@ -870,25 +1246,70 @@
     <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Red Global commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
-    <t>SAINT-GOBAIN</t>
-  </si>
-  <si>
-    <t>FR0000125007</t>
-  </si>
-  <si>
-    <t>NFONVGN05Z0FMN5PEC35</t>
-  </si>
-  <si>
-    <t>Building Products</t>
-  </si>
-  <si>
-    <t>Overall Net-Zero Target Saint-Gobain commits to reach net-zero greenhouse gas emissions across the value chain by 2050 from a 2017 base year*. *Under the former commitment model of the SBTi (available between June 2019 and October 2021), a subset of companies committed to setting near-term science-based targets aligned with well-below 2°C over an interim period as part of their wider netzero commitment (referred to as Option 2 of the Business Ambition for 1.5°C Campaign). There is a strictly enforced timeline for these companies to ratchet ambition to 1.5°C for their near-term targets within a maximum of five years from the time of near-term target validation. At this point, they will be expected to decarbonize in line with their 1.5°C-aligned long-term science-based targets. Near-Term Targets Saint-Gobain commits to reduce absolute scope 1 and 2 GHG emissions 33% by 2030 from a 2017 base year*. Saint-Gobain also commits to reduce absolute scope 3 GHG emissions 16% over the same timeframe from purchased goods and services, fuel and energy related activities, upstream transportation and distribution, business travel, downstream transportation and distribution, and end-of-life treatment of sold products. *The target boundary includes biogenic emissions and removals from bioenergy feedstocks. Long-Term Targets Saint-Gobain commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2017 base year*. Saint-Gobain also commits to reduce absolute scope 3 GHG emissions 90% over the same timeframe. *The target boundary includes biogenic emissions and removals from bioenergy feedstocks.</t>
-  </si>
-  <si>
-    <t>SEKIGUCHI MFG. Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). SEKIGUCHI MFG. Co.,Ltd. commits to reduce scope 1 and scope 2 GHG emissions 50% by 2030 from a 2018 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>ROADGET BUSINESS PTE. LTD.  (owner of the SHEIN brand)</t>
+  </si>
+  <si>
+    <t>254900KJRM13449PP890</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>South-eastern Asia</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target: ROADGET BUSINESS PTE. LTD. commits to reach net-zero greenhouse gas emissions across the value chain by 2050. Near-Term Targets: ROADGET BUSINESS PTE. LTD., owner of the SHEIN brand, commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2023 base year.                 ROADGET BUSINESS PTE. LTD., owner of the SHEIN brand, also commits to increase active annual sourcing of renewable electricity from 72.4% in 2023 to 100% by 2030. ROADGET BUSINESS PTE. LTD., owner of the SHEIN brand, further commits to reduce absolute scope 3 GHG emissions  from purchased goods and services, fuel- and energy-related activities, upstream transportation and distribution, waste generated in operations and end-of-life treatment of sold products 25% by 2030 from a 2023 base year.                  Long-Term Targets: ROADGET BUSINESS PTE. LTD., owner of the SHEIN brand, commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2023 base year. ROADGET BUSINESS PTE. LTD., owner of the SHEIN brand, also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Sainor laboratories Pvt Ltd</t>
+  </si>
+  <si>
+    <t>984500874ACE7D3CEE70</t>
+  </si>
+  <si>
+    <t>FY2035</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Sainor laboratories Pvt Ltd commits to reduce absolute scope 1 and scope 2 GHG emissions 63% by FY2035 from a FY2024 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Schneider Electric</t>
+  </si>
+  <si>
+    <t>FR0000121972</t>
+  </si>
+  <si>
+    <t>969500A1YF1XUYYXS284</t>
+  </si>
+  <si>
+    <t>Overall Net-Zero Target French multinational corporation Schneider Electric commits to reach net zero greenhouse gas emissions across the value chain by 2050 from a 2021 base year. Near-Term Targets French multinational corporation Schneider Electric commits to reduce absolute scope 1 and 2 GHG emissions 76% by 2030 from a 2021 base year. Schneider Electric also commits to increase annual sourcing of renewable electricity from 82% in 2021 to 100% by 2030. Schneider Electric further commits to reduce absolute scope 3 GHG emissions 25% by 2030 from a 2021 base year. Long-Term Targets French multinational corporation Schneider Electric commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2021 base year. Schneider Electric also commits to reduce absolute scope 3 GHG emissions 90% within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits)</t>
+  </si>
+  <si>
+    <t>FY2034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target:
+Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to achieve net-zero greenhouse gas emissions across the value chain by FY2050.
+Near-Term Targets:
+Energy and Industry:
+Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to reduce absolute scope 1 and 2 GHG emissions 48% by FY2030 from a FY2019 base year.* Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel- and energy-related activities, upstream transportation and distribution, waste generated in operations, downstream transportation and distribution and use of sold products 35.0% by FY2034 from a FY2022 base year.* Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) further commits to reduce absolute scope 3 GHG emissions from use of sold products covering distributed fossil fuels 58.8% within the same timeframe.
+FLAG:
+Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to reduce absolute scope 3 FLAG GHG emissions 42.4% by FY2034 from a FY2022 base year.** Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to no deforestation across its primary deforestation-linked commodities, with a target date of December 31, 2025.
+Long-Term Targets:
+Energy and Industry:
+Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to reduce absolute scope 1 and 2 GHG emissions 90.0% by FY2050 from a FY2019 base year.* Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, fuel- and energy-related activities, upstream transportation and distribution, waste generated in operations, downstream transportation and distribution, use of sold products and end-of-life treatment of sold products 90.0% by FY2050 from a FY2022 base year. Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) further commits to reduce absolute scope 3 GHG emissions from use of sold products covering distributed fossil fuels 90.0% within the same timeframe.
+FLAG:
+Schwarz Gruppe (Lidl, Kaufland, Schwarz Produktion, PreZero, Schwarz Digits) commits to reduce absolute scope 3 FLAG GHG emissions 72.0% by FY2050 from a FY2022 base year.**
+*The target boundary includes land-related emissions and removals from biogenic feedstocks. **The target includes FLAG emissions and removals.</t>
+  </si>
+  <si>
+    <t>Sekimae Factory Co., Ltd.</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Sekimae Factory Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2021 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
     <t>Shenzhen First Union Technology Co., Ltd.</t>
@@ -897,50 +1318,114 @@
     <t>SHINEI KOUGYO CO.,LTD</t>
   </si>
   <si>
+    <t>Construction and Engineering</t>
+  </si>
+  <si>
     <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). SHINEI KOUGYO CO.,LTD commits to reduce absolute scope 1 and scope 2 GHG emissions 42% by FY2030 from a FY2023 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
   <si>
-    <t>Solid Rental</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Solid Rental commits to reduce absolute scope 1 and scope 2 GHG emissions 63% by 2035 from a 2025 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Sponda Ltd</t>
-  </si>
-  <si>
-    <t>FI0009006829</t>
-  </si>
-  <si>
-    <t>7437008N02XE409URE26</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Sponda Ltd commits to reduce scope 1 and scope 2 GHG emissions 46% by 2030 from a 2019 base year, and to measure and reduce its scope 3 emissions.</t>
-  </si>
-  <si>
-    <t>Storskogen Group</t>
-  </si>
-  <si>
-    <t>SE0016797732</t>
-  </si>
-  <si>
-    <t>549300DL3K4HLJ41KD24</t>
+    <t>Siemens AG</t>
+  </si>
+  <si>
+    <t>DE0007236101</t>
+  </si>
+  <si>
+    <t>W38RGI023J3WT1HWRP32</t>
   </si>
   <si>
     <t xml:space="preserve">Overall Net-Zero Target: 
-Storskogen Group AB commits to reach net-zero greenhouse gas emissions across the value chain by 2050.
+Siemens AG commits to reach net-zero greenhouse gas emissions across the value chain by FY2050.
 Near-Term Targets: 
-Storskogen Group AB commits to reduce absolute scope 1 and 2 GHG emissions 59% by 2034 from a 2023 base year.* Storskogen Group AB also commits to reduce scope 3 GHG emissions 64% per million SEK value added within the same timeframe.*
-*The target boundary includes land-related emissions and removals from bioenergy feedstocks.
+Siemens AG commits to reduce absolute scope 1 and 2 GHG emissions 90% by FY2030 from a FY2019 base year.* Siemens AG commits to reduce absolute scope 3 GHG emissions 30% within the same timeframe.
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks."
 Long-Term Targets: 
-Storskogen Group AB commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2050 from a 2023 base year.* Storskogen Group AB also commits to reduce scope 3 GHG emissions 97% per million SEK value added within the same timeframe.*
+Siemens AG commits to maintain a minimum of 90% absolute scope 1 and 2 GHG emissions reductions from FY2030 through FY2050 from a FY2019 base year.* Siemens AG commits to reduce absolute scope 3 GHG emissions 90% by FY2050 from a FY2019 base year.
 *The target boundary includes land-related emissions and removals from bioenergy feedstocks.</t>
   </si>
   <si>
-    <t>Financial institutions net-zero commitment: deadline 24 months from Financial Institutions Net-Zero Standard launch</t>
+    <t>Siemens Energy</t>
+  </si>
+  <si>
+    <t>DE000ENER6Y0</t>
+  </si>
+  <si>
+    <t>5299005CHJZ14D4FDJ62</t>
+  </si>
+  <si>
+    <t>Siemens Energy commits to reduce absolute scope 1 and 2 GHG emissions 46% by 2030 from a 2019 base year. Siemens Energy commits to increase annual sourcing of renewable electricity from 59% in 2019 to 100% by 2023. In addition, Siemens Energy commits to reduce absolute scope 3 GHG emissions from use of sold products 28% by 2030 from a 2019 base year.</t>
+  </si>
+  <si>
+    <t>Siemens Gamesa Renewable Energy, S.A.</t>
+  </si>
+  <si>
+    <t>ES0143416115</t>
+  </si>
+  <si>
+    <t>9598004BR8D81D3M1D64</t>
+  </si>
+  <si>
+    <t>Siemens Gamesa Renewable Energy S. A. commits to reduce scope 1 and scope 2 GHG emissions 70% per MW installed by 2025 from a 2017 base year. Siemens Gamesa Renewable Energy S. A. commits that 30% of its suppliers by spend covering purchased goods and services, and transportation and distribution, will have science-based targets by 2025. Siemens Gamesa Renewable Energy S. A. commits to increase annual sourcing of renewable electricity from 58% in 2017 to 100% by 2025.</t>
+  </si>
+  <si>
+    <t>Siemens Healthineers AG</t>
+  </si>
+  <si>
+    <t>DE000SHL1006</t>
+  </si>
+  <si>
+    <t>529900QBVWXMWANH7H45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Siemens Healthineers AG commits to reach net-zero greenhouse gas emissions across the value chain by FY2050. Near-Term Targets: Siemens Healthineers AG commits to reduce absolute scope 1 and 2 GHG emissions 90% by FY2030 from a FY2019 base year.* Siemens Healthineers AG also commits to reduce absolute scope 3 GHG emissions  from purchased goods and services, upstream transportation and distribution, business travel, and use of sold products 28% within the same timeframe. 
+*The target boundary includes land-related emissions and removals from bioenergy feedstocks.   Long-Term Targets: Siemens Healthineers AG commits to maintain a minimum of 90% absolute scope 1 and 2 GHG emissions reductions from FY2030 through FY2050 from a FY2019 base year.* Siemens Healthineers AG also commits to reduce absolute scope 3 GHG emissions from purchased goods and services, upstream transportation and distribution, business travel, and use of sold products 90% by FY2050 from a FY2019 base year.
+ *The target boundary includes land-related emissions and removals from bioenergy feedstocks. </t>
+  </si>
+  <si>
+    <t>Signify</t>
+  </si>
+  <si>
+    <t>NL0011821392</t>
+  </si>
+  <si>
+    <t>549300072P3J1X8NZO35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target
+Signify commits to reach net-zero greenhouse gas emissions across the value chain by
+2040.
+Near-Term Targets
+Signify commits to reduce absolute scope 1 and 2 GHG emissions 50% by 2030 from a 2019
+base year. Signify also commits to reduce absolute scope 3 GHG emissions 50% within the
+same timeframe.
+Long-Term Targets
+Signify commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2040 from a 2019
+base year. Signify also commits to reduce absolute scope 3 GHG emissions 90% within the
+same timeframe.</t>
+  </si>
+  <si>
+    <t>Solo LLC</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Solo LLC commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2020 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Sportler AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Sportler AG commits to reach net-zero greenhouse gas emissions across the value chain by 2045. Near-Term Targets: Sportler AG commits to reduce absolute scope 1 and 2 GHG emissions 47% by 2030 from a 2022 base year.
+Sportler AG commits that 82% of its suppliers by spend covering purchased goods and services will have science-based targets by 2028. 
+Sportler AG also commits to reduce absolute scope 3 GHG emissions from use of sold products for sold fossil fuels 33.6% by 2028 from a 2022 base year.  Long-Term Targets: Sportler AG commits to reduce absolute scope 1 and 2 GHG emissions 90% by 2045 from a 2022 base year.
+Sportler AG commits to reduce absolute scope 3 GHG emissions from use of sold products for sold fossil fuels 90% within the same timeframe.
+Sportler AG also commits to reduce all remaining absolute scope 3 GHG emissions 90% within the same timeframe.</t>
+  </si>
+  <si>
+    <t>Story Contracting Ltd</t>
+  </si>
+  <si>
+    <t>213800VINXFK3OXP8526</t>
+  </si>
+  <si>
+    <t>Story Contracting Ltd commits to reduce absolute scope 1 and 2 GHG emissions by 46.2% by FY2030 from a FY2020 base year. Story Contracting Ltd also commits to increase annual sourcing of renewable electricity from 12% in FY2020 to 100% by FY2025. Story Contracting Ltd further commits to reduce absolute scope 3 GHG emissions 25% by FY2030 from a FY2021 base year. Story Contracting Ltd finally commits that 30% of its suppliers by emissions covering purchased goods and services and waste generated in operations, will have set science-based targets by 2025</t>
   </si>
   <si>
     <t>Swire Coca-Cola Limited</t>
@@ -954,28 +1439,88 @@
 **The target includes FLAG emissions and removals.</t>
   </si>
   <si>
-    <t>Sylvera</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Sylvera commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions. Sylvera commits to reach net-zero by 2035. As part of this, Sylvera commits to reduce scope 1+2+3 emissions 90% by 2035 from a 2022 base year.</t>
-  </si>
-  <si>
-    <t>TOBU TOP TOURS CO.,LTD</t>
-  </si>
-  <si>
-    <t>Hotels, Restaurants and Leisure, and Tourism Services</t>
-  </si>
-  <si>
-    <t>Near-Term Targets: TOBU TOP TOURS CO.,LTD commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2023 base year. TOBU TOP TOURS CO.,LTD also commits to reduce absolute scope 3 GHG emissions 25% within the same timeframe.</t>
-  </si>
-  <si>
-    <t>Trevelyan's Pack and Cool Limited (TPCL)</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Near-Term Targets: Trevelyan's Pack and Cool Limited (TPCL) commits to reduce absolute scope 1 and 2 GHG emissions 42% by 2030 from a 2021 base year. Trevelyan's Pack and Cool Ltd (TPCL) also commits that 80% of its suppliers by spend, covering purchased goods and services, will have SBTs by 2030. Trevelyan's Pack and Cool Ltd (TPCL) further commits that 90.5% of its investments by emissions, will have SBTs within the same timeframe.</t>
+    <t>Swisscom AG</t>
+  </si>
+  <si>
+    <t>CH0008742519</t>
+  </si>
+  <si>
+    <t>5493005SL9HHOXS3B739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net Zero Target
+Swisscom AG commits to reach net-zero greenhouse gas emissions across the value chain by 2035.
+Near-Term Targets
+Swisscom AG commits to reduce absolute scope 1, 2 and 3 GHG emissions 60.7% by 2030
+from a 2018 base year.* Swisscom AG commits to reduce absolute scope 1 and 2 GHG
+emissions 80% by 2030 from a 2018 base year.* Swisscom AG commits to reduce absolute
+scope 3 GHG emissions 60% within the same timeframe.* Swisscom AG further commits to
+continue active annual sourcing of 100% renewable electricity through 2030.
+*The target boundary includes land related emissions and removals from bioenergy
+feedstocks.
+Long-Term Targets
+Swisscom AG commits to reduce absolute scope 1, 2 and 3 GHG emissions 90% by 2035
+from a 2018 base year base year.</t>
+  </si>
+  <si>
+    <t>Symfos Ltd.</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Symfos Ltd. commits to maintain zero scope 1 emissions through 2030. Symfos Ltd. also commits to reduce absolute scope 2 GHG emissions 42% by 2030 from a 2024 base year, and to measure and reduce its scope 3 emissions.</t>
+  </si>
+  <si>
+    <t>Telenor Group</t>
+  </si>
+  <si>
+    <t>NO0010063308</t>
+  </si>
+  <si>
+    <t>549300IM1QSBY4SLPM26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target: Telenor Group commits to reach net-zero greenhouse gas emissions across the value chain by 2045. 
+Near-Term Targets: Telenor Group commits to reduce absolute scope 1 and 2 GHG emissions 69% by 2030 from a 2019 base year. Telenor Group also commits to reduce absolute scope 3 GHG emissions 28% within the same timeframe.
+Long-Term Targets: Telenor Group commits to reduce scope 1, 2 and 3 GHG emissions 90% by 2045 from a 2019 base year.</t>
+  </si>
+  <si>
+    <t>Telia Company</t>
+  </si>
+  <si>
+    <t>SE0000667925</t>
+  </si>
+  <si>
+    <t>213800FSR9RNDUOTXO25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Net-Zero Target:
+Telia Company commits to achieve net-zero greenhouse gas emissions across the value chain by 2040.
+Near-Term Targets:
+Telia Company commits to reduce absolute scope 1 and 2 GHG emissions 90.0% by 2030 from a 2018 base year.* Telia Company also commits to reduce absolute scope 3 GHG emissions 50.0% within the same timeframe.
+Long-Term Targets:
+Telia Company commits to maintain at least 90% absolute scope 1 and 2 emission reductions from 2030 through 2040 from a 2018 base year.* Telia Company also commits to reduce absolute scope 3 GHG emissions 90% by 2040 from a 2018 base year.
+*The target boundary includes land-related emissions and removals from biogenic feedstocks.</t>
+  </si>
+  <si>
+    <t>Tochishu Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Building Products</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Tochishu Co., Ltd. commits to reduce scope 1 and scope 2 GHG emissions 25% by 2030 from a 2020 base year, and to measure and reduce its scope 3 emissions</t>
+  </si>
+  <si>
+    <t>Tri Chemical Laboratories Inc.</t>
+  </si>
+  <si>
+    <t>JP3636000006</t>
+  </si>
+  <si>
+    <t>353800S3OPTEAPIHHJ16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-Term Targets:
+Tri Chemical Laboratories Inc. commits to reduce absolute scope 1 and 2 GHG emissions 42.0% by FY2030 from a FY2024 base year. Tri Chemical Laboratories Inc. also commits to reduce absolute scope 3 GHG emissions 25.0% within the same timeframe.</t>
   </si>
   <si>
     <t>Unilever plc</t>
@@ -997,10 +1542,10 @@
 </t>
   </si>
   <si>
-    <t>Workplace Resource</t>
-  </si>
-  <si>
-    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). Workplace Resource commits to reduce absolute scope 1 and scope 2 GHG emissions 65% by 2035 from a 2023 base year, and to measure and reduce its scope 3 emissions.</t>
+    <t>WORKPLACE SYNERGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>This target was approved using a streamlined target validation route exclusive to small and medium-sized enterprises (SMEs). WORKPLACE SYNERGIES PRIVATE LIMITED commits to reduce scope 1 and scope 2 GHG emissions 42% by 2030 from a 2022 base year, and to measure and reduce its scope 3 emissions.</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1587,7 +2132,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>40019074</v>
+        <v>40013504</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -1611,32 +2156,32 @@
         <v>43</v>
       </c>
       <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>2030</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4">
+        <v>2050</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4">
+        <v>2050</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
       <c r="R4" t="s">
         <v>23</v>
       </c>
@@ -1644,18 +2189,18 @@
         <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U4" t="s">
         <v>23</v>
       </c>
       <c r="V4" s="1">
-        <v>45715.04166666667</v>
+        <v>45631.04166666667</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>40019861</v>
+        <v>40019074</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -1667,25 +2212,25 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
@@ -1703,7 +2248,7 @@
         <v>23</v>
       </c>
       <c r="Q5" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="R5" t="s">
         <v>23</v>
@@ -1712,67 +2257,67 @@
         <v>23</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U5" t="s">
         <v>23</v>
       </c>
       <c r="V5" s="1">
-        <v>45757.04166666667</v>
+        <v>45715.04166666667</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>40010768</v>
+        <v>40019861</v>
       </c>
       <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>23</v>
-      </c>
       <c r="R6" t="s">
         <v>23</v>
       </c>
@@ -1780,134 +2325,134 @@
         <v>23</v>
       </c>
       <c r="T6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V6" s="1">
-        <v>44000.04166666667</v>
+        <v>45757.04166666667</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>40033640</v>
+        <v>40010768</v>
       </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
         <v>58</v>
       </c>
-      <c r="I7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>2036</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>59</v>
-      </c>
-      <c r="R7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S7" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U7" t="s">
-        <v>23</v>
-      </c>
       <c r="V7" s="1">
-        <v>46303.04166666667</v>
+        <v>44000.04166666667</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>40008484</v>
+        <v>40016561</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8">
+        <v>2035</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="s">
         <v>62</v>
-      </c>
-      <c r="G8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8">
-        <v>2030</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>65</v>
       </c>
       <c r="R8" t="s">
         <v>23</v>
@@ -1927,28 +2472,28 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>40021798</v>
+        <v>40008484</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -1956,26 +2501,26 @@
       <c r="J9" t="s">
         <v>30</v>
       </c>
-      <c r="K9" t="s">
-        <v>50</v>
+      <c r="K9">
+        <v>2030</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P9" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R9" t="s">
         <v>23</v>
@@ -1990,15 +2535,15 @@
         <v>23</v>
       </c>
       <c r="V9" s="1">
-        <v>45960.04166666667</v>
+        <v>45974.04166666667</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>40011175</v>
+        <v>40014227</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -2010,13 +2555,13 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
         <v>39</v>
@@ -2046,7 +2591,7 @@
         <v>23</v>
       </c>
       <c r="R10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="S10" s="1">
         <v>44614.04166666667</v>
@@ -2055,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="U10" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="V10" s="1">
         <v>44614.04166666667</v>
@@ -2063,55 +2608,55 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>40000194</v>
+        <v>40006125</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="K11">
+        <v>2030</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N11">
+        <v>2040</v>
       </c>
       <c r="O11" t="s">
-        <v>23</v>
-      </c>
-      <c r="P11" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P11">
+        <v>2040</v>
       </c>
       <c r="Q11" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="R11" t="s">
         <v>23</v>
@@ -2120,89 +2665,89 @@
         <v>23</v>
       </c>
       <c r="T11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U11" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V11" s="1">
-        <v>45253.04166666667</v>
+        <v>45841.04166666667</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>40013805</v>
+        <v>40021798</v>
       </c>
       <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="O12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>23</v>
-      </c>
       <c r="R12" t="s">
-        <v>76</v>
-      </c>
-      <c r="S12" s="1">
-        <v>44228.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S12" t="s">
+        <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U12" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="V12" s="1">
-        <v>44228.04166666667</v>
+        <v>45960.04166666667</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>40016585</v>
+        <v>40011175</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -2214,16 +2759,16 @@
         <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s">
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J13" t="s">
         <v>23</v>
@@ -2241,7 +2786,7 @@
         <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P13" t="s">
         <v>23</v>
@@ -2250,113 +2795,113 @@
         <v>23</v>
       </c>
       <c r="R13" t="s">
-        <v>23</v>
-      </c>
-      <c r="S13" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S13" s="1">
+        <v>44614.04166666667</v>
       </c>
       <c r="T13" t="s">
         <v>23</v>
       </c>
       <c r="U13" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="V13" s="1">
-        <v>45596.04166666667</v>
+        <v>44614.04166666667</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>40000694</v>
+        <v>40040240</v>
       </c>
       <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
         <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14">
-        <v>2030</v>
+        <v>23</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>30</v>
-      </c>
-      <c r="N14">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="N14" t="s">
+        <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="P14" t="s">
+        <v>23</v>
       </c>
       <c r="Q14" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="R14" t="s">
-        <v>76</v>
-      </c>
-      <c r="S14" s="1">
-        <v>44777.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S14" t="s">
+        <v>23</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U14" t="s">
         <v>23</v>
       </c>
       <c r="V14" s="1">
-        <v>45617.04166666667</v>
+        <v>46289.04166666667</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>40001271</v>
+        <v>40013805</v>
       </c>
       <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" t="s">
         <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" t="s">
-        <v>95</v>
       </c>
       <c r="I15" t="s">
         <v>39</v>
@@ -2377,7 +2922,7 @@
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P15" t="s">
         <v>23</v>
@@ -2386,27 +2931,27 @@
         <v>23</v>
       </c>
       <c r="R15" t="s">
-        <v>23</v>
-      </c>
-      <c r="S15" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S15" s="1">
+        <v>44228.04166666667</v>
       </c>
       <c r="T15" t="s">
         <v>23</v>
       </c>
       <c r="U15" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="V15" s="1">
-        <v>45253.04166666667</v>
+        <v>44228.04166666667</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>40030180</v>
+        <v>40016585</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -2418,22 +2963,22 @@
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J16" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16">
-        <v>2030</v>
+        <v>23</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
       </c>
       <c r="L16" t="s">
         <v>23</v>
@@ -2451,7 +2996,7 @@
         <v>23</v>
       </c>
       <c r="Q16" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="R16" t="s">
         <v>23</v>
@@ -2460,39 +3005,39 @@
         <v>23</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U16" t="s">
         <v>23</v>
       </c>
       <c r="V16" s="1">
-        <v>46184.04166666667</v>
+        <v>45596.04166666667</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>40006773</v>
+        <v>40010685</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
         <v>29</v>
@@ -2500,8 +3045,8 @@
       <c r="J17" t="s">
         <v>30</v>
       </c>
-      <c r="K17">
-        <v>2030</v>
+      <c r="K17" t="s">
+        <v>53</v>
       </c>
       <c r="L17" t="s">
         <v>29</v>
@@ -2509,23 +3054,23 @@
       <c r="M17" t="s">
         <v>30</v>
       </c>
-      <c r="N17">
-        <v>2040</v>
+      <c r="N17" t="s">
+        <v>80</v>
       </c>
       <c r="O17" t="s">
         <v>29</v>
       </c>
-      <c r="P17">
-        <v>2040</v>
+      <c r="P17" t="s">
+        <v>80</v>
       </c>
       <c r="Q17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R17" t="s">
-        <v>76</v>
-      </c>
-      <c r="S17" s="1">
-        <v>44136.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S17" t="s">
+        <v>23</v>
       </c>
       <c r="T17" t="s">
         <v>32</v>
@@ -2534,101 +3079,101 @@
         <v>23</v>
       </c>
       <c r="V17" s="1">
-        <v>46149.04166666667</v>
+        <v>45554.04166666667</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>40002296</v>
+        <v>40000694</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="I18" t="s">
         <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="K18">
         <v>2030</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N18">
+        <v>2050</v>
       </c>
       <c r="O18" t="s">
-        <v>23</v>
-      </c>
-      <c r="P18" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P18">
+        <v>2050</v>
       </c>
       <c r="Q18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="R18" t="s">
-        <v>23</v>
-      </c>
-      <c r="S18" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S18" s="1">
+        <v>44777.04166666667</v>
       </c>
       <c r="T18" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="U18" t="s">
         <v>23</v>
       </c>
       <c r="V18" s="1">
-        <v>43993.04166666667</v>
+        <v>45617.04166666667</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>40014084</v>
+        <v>40013474</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
         <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
         <v>29</v>
@@ -2640,45 +3185,45 @@
         <v>2030</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19">
-        <v>2040</v>
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>29</v>
-      </c>
-      <c r="P19">
-        <v>2040</v>
+        <v>39</v>
+      </c>
+      <c r="P19" t="s">
+        <v>23</v>
       </c>
       <c r="Q19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="R19" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="S19" s="1">
-        <v>44317.04166666667</v>
+        <v>44348.04166666667</v>
       </c>
       <c r="T19" t="s">
         <v>32</v>
       </c>
       <c r="U19" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="V19" s="1">
-        <v>45666.04166666667</v>
+        <v>44406.04166666667</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>40006529</v>
+        <v>40010939</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -2687,16 +3232,16 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
         <v>29</v>
@@ -2723,7 +3268,7 @@
         <v>23</v>
       </c>
       <c r="Q20" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="R20" t="s">
         <v>23</v>
@@ -2738,33 +3283,33 @@
         <v>23</v>
       </c>
       <c r="V20" s="1">
-        <v>45519.04166666667</v>
+        <v>45561.04166666667</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>40005566</v>
+        <v>40013885</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
         <v>29</v>
@@ -2773,7 +3318,7 @@
         <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L21" t="s">
         <v>29</v>
@@ -2782,22 +3327,22 @@
         <v>30</v>
       </c>
       <c r="N21" t="s">
+        <v>114</v>
+      </c>
+      <c r="O21" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>115</v>
+      </c>
+      <c r="R21" t="s">
         <v>71</v>
       </c>
-      <c r="O21" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>119</v>
-      </c>
-      <c r="R21" t="s">
-        <v>76</v>
-      </c>
       <c r="S21" s="1">
-        <v>43709.04166666667</v>
+        <v>44462.04166666667</v>
       </c>
       <c r="T21" t="s">
         <v>32</v>
@@ -2806,33 +3351,33 @@
         <v>23</v>
       </c>
       <c r="V21" s="1">
-        <v>45414.04166666667</v>
+        <v>44763.04166666667</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>40001732</v>
+        <v>40006773</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
         <v>29</v>
@@ -2844,72 +3389,72 @@
         <v>2030</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N22">
+        <v>2040</v>
       </c>
       <c r="O22" t="s">
-        <v>39</v>
-      </c>
-      <c r="P22" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P22">
+        <v>2040</v>
       </c>
       <c r="Q22" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="R22" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="S22" s="1">
-        <v>43678.04166666667</v>
+        <v>44136.04166666667</v>
       </c>
       <c r="T22" t="s">
         <v>32</v>
       </c>
       <c r="U22" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V22" s="1">
-        <v>43678.04166666667</v>
+        <v>46149.04166666667</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>40012170</v>
+        <v>40002296</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="K23">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="L23" t="s">
         <v>23</v>
@@ -2927,7 +3472,7 @@
         <v>23</v>
       </c>
       <c r="Q23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="R23" t="s">
         <v>23</v>
@@ -2936,39 +3481,39 @@
         <v>23</v>
       </c>
       <c r="T23" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="U23" t="s">
         <v>23</v>
       </c>
       <c r="V23" s="1">
-        <v>46282.04166666667</v>
+        <v>43993.04166666667</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>40028281</v>
+        <v>40014084</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s">
         <v>29</v>
@@ -2977,31 +3522,31 @@
         <v>30</v>
       </c>
       <c r="K24">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N24">
+        <v>2040</v>
       </c>
       <c r="O24" t="s">
-        <v>23</v>
-      </c>
-      <c r="P24" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P24">
+        <v>2040</v>
       </c>
       <c r="Q24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R24" t="s">
-        <v>23</v>
-      </c>
-      <c r="S24" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S24" s="1">
+        <v>44317.04166666667</v>
       </c>
       <c r="T24" t="s">
         <v>32</v>
@@ -3010,15 +3555,15 @@
         <v>23</v>
       </c>
       <c r="V24" s="1">
-        <v>46030.04166666667</v>
+        <v>45666.04166666667</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>40001238</v>
+        <v>40018262</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -3027,16 +3572,16 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I25" t="s">
         <v>29</v>
@@ -3063,7 +3608,7 @@
         <v>23</v>
       </c>
       <c r="Q25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R25" t="s">
         <v>23</v>
@@ -3078,33 +3623,33 @@
         <v>23</v>
       </c>
       <c r="V25" s="1">
-        <v>45001.04166666667</v>
+        <v>45792.04166666667</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>40000473</v>
+        <v>40009556</v>
       </c>
       <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" t="s">
         <v>137</v>
-      </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" t="s">
-        <v>139</v>
       </c>
       <c r="I26" t="s">
         <v>29</v>
@@ -3116,22 +3661,22 @@
         <v>2030</v>
       </c>
       <c r="L26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26">
-        <v>2045</v>
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>29</v>
-      </c>
-      <c r="P26">
-        <v>2045</v>
+        <v>23</v>
+      </c>
+      <c r="P26" t="s">
+        <v>23</v>
       </c>
       <c r="Q26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R26" t="s">
         <v>23</v>
@@ -3146,66 +3691,66 @@
         <v>23</v>
       </c>
       <c r="V26" s="1">
-        <v>45302.04166666667</v>
+        <v>45365.04166666667</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>40023357</v>
+        <v>40005566</v>
       </c>
       <c r="B27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
         <v>141</v>
       </c>
-      <c r="C27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" t="s">
-        <v>47</v>
-      </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
+        <v>80</v>
+      </c>
+      <c r="O27" t="s">
+        <v>29</v>
+      </c>
+      <c r="P27" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q27" t="s">
         <v>142</v>
       </c>
-      <c r="I27" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N27" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" t="s">
-        <v>23</v>
-      </c>
-      <c r="P27" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>143</v>
-      </c>
       <c r="R27" t="s">
-        <v>23</v>
-      </c>
-      <c r="S27" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S27" s="1">
+        <v>43709.04166666667</v>
       </c>
       <c r="T27" t="s">
         <v>32</v>
@@ -3214,33 +3759,33 @@
         <v>23</v>
       </c>
       <c r="V27" s="1">
-        <v>45820.04166666667</v>
+        <v>45414.04166666667</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>40006997</v>
+        <v>40003668</v>
       </c>
       <c r="B28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
         <v>144</v>
       </c>
-      <c r="C28" t="s">
-        <v>23</v>
-      </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s">
         <v>29</v>
@@ -3252,48 +3797,48 @@
         <v>2030</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
-      </c>
-      <c r="N28" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N28">
+        <v>2040</v>
       </c>
       <c r="O28" t="s">
-        <v>39</v>
-      </c>
-      <c r="P28" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P28">
+        <v>2040</v>
       </c>
       <c r="Q28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="S28" s="1">
-        <v>43923.04166666667</v>
+        <v>43709.04166666667</v>
       </c>
       <c r="T28" t="s">
         <v>32</v>
       </c>
       <c r="U28" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V28" s="1">
-        <v>44238.04166666667</v>
+        <v>45330.04166666667</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>40001665</v>
+        <v>40025147</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
@@ -3302,22 +3847,22 @@
         <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="G29" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J29" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K29" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L29" t="s">
         <v>23</v>
@@ -3335,7 +3880,7 @@
         <v>23</v>
       </c>
       <c r="Q29" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="R29" t="s">
         <v>23</v>
@@ -3344,39 +3889,39 @@
         <v>23</v>
       </c>
       <c r="T29" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U29" t="s">
         <v>23</v>
       </c>
       <c r="V29" s="1">
-        <v>45645.04166666667</v>
+        <v>45813.04166666667</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>40005992</v>
+        <v>40011861</v>
       </c>
       <c r="B30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" t="s">
         <v>150</v>
       </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="E30" t="s">
         <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="I30" t="s">
         <v>29</v>
@@ -3403,7 +3948,7 @@
         <v>23</v>
       </c>
       <c r="Q30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R30" t="s">
         <v>23</v>
@@ -3418,66 +3963,66 @@
         <v>23</v>
       </c>
       <c r="V30" s="1">
-        <v>45519.04166666667</v>
+        <v>45554.04166666667</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>40015837</v>
+        <v>40028879</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" t="s">
         <v>155</v>
       </c>
-      <c r="G31" t="s">
-        <v>63</v>
-      </c>
-      <c r="H31" t="s">
-        <v>70</v>
-      </c>
       <c r="I31" t="s">
         <v>29</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
       </c>
-      <c r="K31" t="s">
-        <v>50</v>
+      <c r="K31">
+        <v>2030</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" t="s">
         <v>156</v>
       </c>
-      <c r="O31" t="s">
-        <v>29</v>
-      </c>
-      <c r="P31" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>157</v>
-      </c>
       <c r="R31" t="s">
-        <v>76</v>
-      </c>
-      <c r="S31" s="1">
-        <v>43952.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S31" t="s">
+        <v>23</v>
       </c>
       <c r="T31" t="s">
         <v>32</v>
@@ -3486,33 +4031,33 @@
         <v>23</v>
       </c>
       <c r="V31" s="1">
-        <v>44826.04166666667</v>
+        <v>46184.04166666667</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>40032031</v>
+        <v>40009166</v>
       </c>
       <c r="B32" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" t="s">
         <v>158</v>
       </c>
-      <c r="C32" t="s">
-        <v>23</v>
-      </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
-        <v>159</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
         <v>29</v>
@@ -3520,32 +4065,32 @@
       <c r="J32" t="s">
         <v>30</v>
       </c>
-      <c r="K32">
-        <v>2030</v>
+      <c r="K32" t="s">
+        <v>53</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="O32" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P32" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="Q32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="R32" t="s">
-        <v>23</v>
-      </c>
-      <c r="S32" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S32" s="1">
+        <v>43709.04166666667</v>
       </c>
       <c r="T32" t="s">
         <v>32</v>
@@ -3554,33 +4099,33 @@
         <v>23</v>
       </c>
       <c r="V32" s="1">
-        <v>46121.04166666667</v>
+        <v>45316.04166666667</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>40003990</v>
+        <v>40004069</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="I33" t="s">
         <v>29</v>
@@ -3588,8 +4133,8 @@
       <c r="J33" t="s">
         <v>30</v>
       </c>
-      <c r="K33" t="s">
-        <v>50</v>
+      <c r="K33">
+        <v>2030</v>
       </c>
       <c r="L33" t="s">
         <v>29</v>
@@ -3597,23 +4142,23 @@
       <c r="M33" t="s">
         <v>30</v>
       </c>
-      <c r="N33" t="s">
+      <c r="N33">
+        <v>2050</v>
+      </c>
+      <c r="O33" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33">
+        <v>2050</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>166</v>
+      </c>
+      <c r="R33" t="s">
         <v>71</v>
       </c>
-      <c r="O33" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>163</v>
-      </c>
-      <c r="R33" t="s">
-        <v>76</v>
-      </c>
       <c r="S33" s="1">
-        <v>43709.04166666667</v>
+        <v>44399.04166666667</v>
       </c>
       <c r="T33" t="s">
         <v>32</v>
@@ -3622,15 +4167,15 @@
         <v>23</v>
       </c>
       <c r="V33" s="1">
-        <v>45484.04166666667</v>
+        <v>45519.04166666667</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>40024609</v>
+        <v>40002869</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -3639,17 +4184,17 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>168</v>
+      </c>
+      <c r="G34" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" t="s">
         <v>46</v>
       </c>
-      <c r="F34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s">
-        <v>38</v>
-      </c>
       <c r="I34" t="s">
         <v>29</v>
       </c>
@@ -3657,7 +4202,7 @@
         <v>30</v>
       </c>
       <c r="K34">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
@@ -3675,7 +4220,7 @@
         <v>23</v>
       </c>
       <c r="Q34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="R34" t="s">
         <v>23</v>
@@ -3690,33 +4235,33 @@
         <v>23</v>
       </c>
       <c r="V34" s="1">
-        <v>46212.04166666667</v>
+        <v>45477.04166666667</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>40007044</v>
+        <v>40000473</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F35" t="s">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
@@ -3724,8 +4269,8 @@
       <c r="J35" t="s">
         <v>30</v>
       </c>
-      <c r="K35" t="s">
-        <v>50</v>
+      <c r="K35">
+        <v>2030</v>
       </c>
       <c r="L35" t="s">
         <v>29</v>
@@ -3733,23 +4278,23 @@
       <c r="M35" t="s">
         <v>30</v>
       </c>
-      <c r="N35" t="s">
-        <v>156</v>
+      <c r="N35">
+        <v>2045</v>
       </c>
       <c r="O35" t="s">
         <v>29</v>
       </c>
-      <c r="P35" t="s">
-        <v>156</v>
+      <c r="P35">
+        <v>2045</v>
       </c>
       <c r="Q35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R35" t="s">
-        <v>76</v>
-      </c>
-      <c r="S35" s="1">
-        <v>43952.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S35" t="s">
+        <v>23</v>
       </c>
       <c r="T35" t="s">
         <v>32</v>
@@ -3758,33 +4303,33 @@
         <v>23</v>
       </c>
       <c r="V35" s="1">
-        <v>45589.04166666667</v>
+        <v>45302.04166666667</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>40001186</v>
+        <v>40028855</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
         <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F36" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
         <v>29</v>
@@ -3793,31 +4338,31 @@
         <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P36" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="Q36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R36" t="s">
-        <v>76</v>
-      </c>
-      <c r="S36" s="1">
-        <v>43709.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S36" t="s">
+        <v>23</v>
       </c>
       <c r="T36" t="s">
         <v>32</v>
@@ -3826,33 +4371,33 @@
         <v>23</v>
       </c>
       <c r="V36" s="1">
-        <v>45456.04166666667</v>
+        <v>46009.04166666667</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>40002531</v>
+        <v>40007442</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="G37" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I37" t="s">
         <v>29</v>
@@ -3861,31 +4406,31 @@
         <v>30</v>
       </c>
       <c r="K37">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
-      </c>
-      <c r="N37" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N37">
+        <v>2050</v>
       </c>
       <c r="O37" t="s">
-        <v>23</v>
-      </c>
-      <c r="P37" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P37">
+        <v>2050</v>
       </c>
       <c r="Q37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R37" t="s">
-        <v>23</v>
-      </c>
-      <c r="S37" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S37" s="1">
+        <v>44826.04166666667</v>
       </c>
       <c r="T37" t="s">
         <v>32</v>
@@ -3894,33 +4439,33 @@
         <v>23</v>
       </c>
       <c r="V37" s="1">
-        <v>44434.04166666667</v>
+        <v>45666.04166666667</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>40010135</v>
+        <v>40011673</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="H38" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="I38" t="s">
         <v>29</v>
@@ -3928,8 +4473,8 @@
       <c r="J38" t="s">
         <v>30</v>
       </c>
-      <c r="K38" t="s">
-        <v>180</v>
+      <c r="K38">
+        <v>2030</v>
       </c>
       <c r="L38" t="s">
         <v>29</v>
@@ -3937,23 +4482,23 @@
       <c r="M38" t="s">
         <v>30</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N38">
+        <v>2050</v>
+      </c>
+      <c r="O38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38">
+        <v>2050</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>182</v>
+      </c>
+      <c r="R38" t="s">
         <v>71</v>
       </c>
-      <c r="O38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>181</v>
-      </c>
-      <c r="R38" t="s">
-        <v>76</v>
-      </c>
       <c r="S38" s="1">
-        <v>45015.04166666667</v>
+        <v>44728.04166666667</v>
       </c>
       <c r="T38" t="s">
         <v>32</v>
@@ -3962,101 +4507,101 @@
         <v>23</v>
       </c>
       <c r="V38" s="1">
-        <v>45337.04166666667</v>
+        <v>45645.04166666667</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>40037107</v>
+        <v>40009345</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" t="s">
         <v>184</v>
       </c>
-      <c r="E39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="I39" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" t="s">
         <v>185</v>
       </c>
-      <c r="G39" t="s">
+      <c r="K39">
+        <v>2030</v>
+      </c>
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" t="s">
         <v>186</v>
       </c>
-      <c r="H39" t="s">
-        <v>70</v>
-      </c>
-      <c r="I39" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" t="s">
-        <v>30</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="R39" t="s">
+        <v>23</v>
+      </c>
+      <c r="S39" t="s">
+        <v>23</v>
+      </c>
+      <c r="T39" t="s">
         <v>187</v>
       </c>
-      <c r="L39" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" t="s">
-        <v>23</v>
-      </c>
-      <c r="P39" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>188</v>
-      </c>
-      <c r="R39" t="s">
-        <v>23</v>
-      </c>
-      <c r="S39" t="s">
-        <v>23</v>
-      </c>
-      <c r="T39" t="s">
-        <v>32</v>
-      </c>
       <c r="U39" t="s">
         <v>23</v>
       </c>
       <c r="V39" s="1">
-        <v>46289.04166666667</v>
+        <v>43790.04166666667</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>40028213</v>
+        <v>40015837</v>
       </c>
       <c r="B40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" t="s">
         <v>189</v>
       </c>
-      <c r="C40" t="s">
-        <v>23</v>
-      </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H40" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="I40" t="s">
         <v>29</v>
@@ -4064,32 +4609,32 @@
       <c r="J40" t="s">
         <v>30</v>
       </c>
-      <c r="K40">
-        <v>2034</v>
+      <c r="K40" t="s">
+        <v>53</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="O40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P40" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="Q40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R40" t="s">
-        <v>23</v>
-      </c>
-      <c r="S40" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S40" s="1">
+        <v>43952.04166666667</v>
       </c>
       <c r="T40" t="s">
         <v>32</v>
@@ -4098,101 +4643,101 @@
         <v>23</v>
       </c>
       <c r="V40" s="1">
-        <v>46030.04166666667</v>
+        <v>44826.04166666667</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40001521</v>
+        <v>40009546</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="I41" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J41" t="s">
-        <v>30</v>
-      </c>
-      <c r="K41">
-        <v>2030</v>
+        <v>23</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>30</v>
-      </c>
-      <c r="N41">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="N41" t="s">
+        <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>29</v>
-      </c>
-      <c r="P41">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="P41" t="s">
+        <v>23</v>
       </c>
       <c r="Q41" t="s">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="R41" t="s">
-        <v>76</v>
-      </c>
-      <c r="S41" s="1">
+        <v>23</v>
+      </c>
+      <c r="S41" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" t="s">
+        <v>23</v>
+      </c>
+      <c r="U41" t="s">
+        <v>58</v>
+      </c>
+      <c r="V41" s="1">
         <v>44931.04166666667</v>
-      </c>
-      <c r="T41" t="s">
-        <v>32</v>
-      </c>
-      <c r="U41" t="s">
-        <v>23</v>
-      </c>
-      <c r="V41" s="1">
-        <v>45617.04166666667</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>40005832</v>
+        <v>40000722</v>
       </c>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
         <v>29</v>
@@ -4200,32 +4745,32 @@
       <c r="J42" t="s">
         <v>30</v>
       </c>
-      <c r="K42">
-        <v>2030</v>
+      <c r="K42" t="s">
+        <v>53</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="O42" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P42" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="Q42" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="R42" t="s">
-        <v>23</v>
-      </c>
-      <c r="S42" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S42" s="1">
+        <v>43647.04166666667</v>
       </c>
       <c r="T42" t="s">
         <v>32</v>
@@ -4234,15 +4779,15 @@
         <v>23</v>
       </c>
       <c r="V42" s="1">
-        <v>44770.04166666667</v>
+        <v>44763.04166666667</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>40004458</v>
+        <v>40016076</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
@@ -4251,16 +4796,16 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="G43" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="H43" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="I43" t="s">
         <v>29</v>
@@ -4287,7 +4832,7 @@
         <v>23</v>
       </c>
       <c r="Q43" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R43" t="s">
         <v>23</v>
@@ -4302,33 +4847,33 @@
         <v>23</v>
       </c>
       <c r="V43" s="1">
-        <v>45134.04166666667</v>
+        <v>45400.04166666667</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>40025590</v>
+        <v>40005167</v>
       </c>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G44" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s">
-        <v>199</v>
+        <v>61</v>
       </c>
       <c r="I44" t="s">
         <v>29</v>
@@ -4337,31 +4882,31 @@
         <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="O44" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P44" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="Q44" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="R44" t="s">
-        <v>23</v>
-      </c>
-      <c r="S44" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S44" s="1">
+        <v>44315.04166666667</v>
       </c>
       <c r="T44" t="s">
         <v>32</v>
@@ -4370,33 +4915,33 @@
         <v>23</v>
       </c>
       <c r="V44" s="1">
-        <v>45876.04166666667</v>
+        <v>45638.04166666667</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>40001122</v>
+        <v>40009331</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="G45" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="H45" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="I45" t="s">
         <v>29</v>
@@ -4408,28 +4953,28 @@
         <v>2030</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
-      </c>
-      <c r="N45" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N45">
+        <v>2039</v>
       </c>
       <c r="O45" t="s">
-        <v>23</v>
-      </c>
-      <c r="P45" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P45">
+        <v>2039</v>
       </c>
       <c r="Q45" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="R45" t="s">
-        <v>23</v>
-      </c>
-      <c r="S45" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S45" s="1">
+        <v>43647.04166666667</v>
       </c>
       <c r="T45" t="s">
         <v>32</v>
@@ -4438,101 +4983,101 @@
         <v>23</v>
       </c>
       <c r="V45" s="1">
-        <v>45603.04166666667</v>
+        <v>44875.04166666667</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>40004941</v>
+        <v>40003990</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C46" t="s">
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H46" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
         <v>29</v>
       </c>
       <c r="J46" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46">
-        <v>2028</v>
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
+        <v>53</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="O46" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P46" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="Q46" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="R46" t="s">
-        <v>23</v>
-      </c>
-      <c r="S46" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S46" s="1">
+        <v>43709.04166666667</v>
       </c>
       <c r="T46" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="U46" t="s">
         <v>23</v>
       </c>
       <c r="V46" s="1">
-        <v>44735.04166666667</v>
+        <v>45484.04166666667</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>40005117</v>
+        <v>40010691</v>
       </c>
       <c r="B47" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="D47" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="G47" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="H47" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="I47" t="s">
         <v>29</v>
@@ -4540,135 +5085,135 @@
       <c r="J47" t="s">
         <v>30</v>
       </c>
-      <c r="K47">
-        <v>2030</v>
+      <c r="K47" t="s">
+        <v>220</v>
       </c>
       <c r="L47" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>30</v>
-      </c>
-      <c r="N47">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="N47" t="s">
+        <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>29</v>
-      </c>
-      <c r="P47">
-        <v>2050</v>
+        <v>47</v>
+      </c>
+      <c r="P47" t="s">
+        <v>23</v>
       </c>
       <c r="Q47" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="R47" t="s">
-        <v>76</v>
-      </c>
-      <c r="S47" s="1">
-        <v>44000.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S47" t="s">
+        <v>23</v>
       </c>
       <c r="T47" t="s">
         <v>32</v>
       </c>
       <c r="U47" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V47" s="1">
-        <v>45841.04166666667</v>
+        <v>46268.04166666667</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>40016681</v>
+        <v>40007044</v>
       </c>
       <c r="B48" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H48" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="O48" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P48" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="Q48" t="s">
-        <v>23</v>
+        <v>225</v>
       </c>
       <c r="R48" t="s">
-        <v>23</v>
-      </c>
-      <c r="S48" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S48" s="1">
+        <v>43952.04166666667</v>
       </c>
       <c r="T48" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U48" t="s">
         <v>23</v>
       </c>
       <c r="V48" s="1">
-        <v>45624.04166666667</v>
+        <v>45589.04166666667</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>40025133</v>
+        <v>40001186</v>
       </c>
       <c r="B49" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="E49" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
         <v>29</v>
@@ -4677,31 +5222,31 @@
         <v>30</v>
       </c>
       <c r="K49" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="O49" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P49" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="Q49" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="R49" t="s">
-        <v>23</v>
-      </c>
-      <c r="S49" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S49" s="1">
+        <v>43709.04166666667</v>
       </c>
       <c r="T49" t="s">
         <v>32</v>
@@ -4710,15 +5255,15 @@
         <v>23</v>
       </c>
       <c r="V49" s="1">
-        <v>45869.04166666667</v>
+        <v>45456.04166666667</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>40000463</v>
+        <v>40000458</v>
       </c>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C50" t="s">
         <v>23</v>
@@ -4730,13 +5275,13 @@
         <v>25</v>
       </c>
       <c r="F50" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H50" t="s">
-        <v>214</v>
+        <v>67</v>
       </c>
       <c r="I50" t="s">
         <v>39</v>
@@ -4766,45 +5311,45 @@
         <v>23</v>
       </c>
       <c r="R50" t="s">
-        <v>23</v>
-      </c>
-      <c r="S50" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S50" s="1">
+        <v>44136.04166666667</v>
       </c>
       <c r="T50" t="s">
         <v>23</v>
       </c>
       <c r="U50" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="V50" s="1">
-        <v>45330.04166666667</v>
+        <v>44136.04166666667</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>40009928</v>
+        <v>40003276</v>
       </c>
       <c r="B51" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>216</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F51" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="H51" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="I51" t="s">
         <v>29</v>
@@ -4816,28 +5361,28 @@
         <v>2030</v>
       </c>
       <c r="L51" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>30</v>
-      </c>
-      <c r="N51">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="N51" t="s">
+        <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>29</v>
-      </c>
-      <c r="P51">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="P51" t="s">
+        <v>23</v>
       </c>
       <c r="Q51" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="R51" t="s">
-        <v>76</v>
-      </c>
-      <c r="S51" s="1">
-        <v>43709.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S51" t="s">
+        <v>23</v>
       </c>
       <c r="T51" t="s">
         <v>32</v>
@@ -4846,15 +5391,15 @@
         <v>23</v>
       </c>
       <c r="V51" s="1">
-        <v>45267.04166666667</v>
+        <v>45260.04166666667</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>40011125</v>
+        <v>40006857</v>
       </c>
       <c r="B52" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -4863,16 +5408,16 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="H52" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="I52" t="s">
         <v>29</v>
@@ -4884,22 +5429,22 @@
         <v>2030</v>
       </c>
       <c r="L52" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>30</v>
-      </c>
-      <c r="N52">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="N52" t="s">
+        <v>23</v>
       </c>
       <c r="O52" t="s">
-        <v>29</v>
-      </c>
-      <c r="P52">
-        <v>2050</v>
+        <v>23</v>
+      </c>
+      <c r="P52" t="s">
+        <v>23</v>
       </c>
       <c r="Q52" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="R52" t="s">
         <v>23</v>
@@ -4914,15 +5459,15 @@
         <v>23</v>
       </c>
       <c r="V52" s="1">
-        <v>45484.04166666667</v>
+        <v>45239.04166666667</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>40021364</v>
+        <v>40027311</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -4934,22 +5479,22 @@
         <v>25</v>
       </c>
       <c r="F53" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="H53" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="I53" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s">
-        <v>30</v>
-      </c>
-      <c r="K53">
-        <v>2030</v>
+        <v>23</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
       </c>
       <c r="L53" t="s">
         <v>23</v>
@@ -4967,7 +5512,7 @@
         <v>23</v>
       </c>
       <c r="Q53" t="s">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="R53" t="s">
         <v>23</v>
@@ -4976,107 +5521,107 @@
         <v>23</v>
       </c>
       <c r="T53" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U53" t="s">
         <v>23</v>
       </c>
       <c r="V53" s="1">
-        <v>45974.04166666667</v>
+        <v>45918.04166666667</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>40029724</v>
+        <v>40001598</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="H54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" t="s">
+        <v>23</v>
+      </c>
+      <c r="O54" t="s">
+        <v>39</v>
+      </c>
+      <c r="P54" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>23</v>
+      </c>
+      <c r="R54" t="s">
+        <v>71</v>
+      </c>
+      <c r="S54" s="1">
+        <v>44256.04166666667</v>
+      </c>
+      <c r="T54" t="s">
+        <v>23</v>
+      </c>
+      <c r="U54" t="s">
         <v>58</v>
       </c>
-      <c r="I54" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" t="s">
-        <v>30</v>
-      </c>
-      <c r="K54" t="s">
-        <v>50</v>
-      </c>
-      <c r="L54" t="s">
-        <v>23</v>
-      </c>
-      <c r="M54" t="s">
-        <v>23</v>
-      </c>
-      <c r="N54" t="s">
-        <v>23</v>
-      </c>
-      <c r="O54" t="s">
-        <v>23</v>
-      </c>
-      <c r="P54" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>226</v>
-      </c>
-      <c r="R54" t="s">
-        <v>23</v>
-      </c>
-      <c r="S54" t="s">
-        <v>23</v>
-      </c>
-      <c r="T54" t="s">
-        <v>32</v>
-      </c>
-      <c r="U54" t="s">
-        <v>23</v>
-      </c>
       <c r="V54" s="1">
-        <v>46289.04166666667</v>
+        <v>44256.04166666667</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>40011442</v>
+        <v>40014694</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E55" t="s">
         <v>25</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H55" t="s">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="I55" t="s">
         <v>29</v>
@@ -5084,8 +5629,8 @@
       <c r="J55" t="s">
         <v>30</v>
       </c>
-      <c r="K55">
-        <v>2030</v>
+      <c r="K55" t="s">
+        <v>53</v>
       </c>
       <c r="L55" t="s">
         <v>29</v>
@@ -5093,23 +5638,23 @@
       <c r="M55" t="s">
         <v>30</v>
       </c>
-      <c r="N55">
-        <v>2050</v>
+      <c r="N55" t="s">
+        <v>114</v>
       </c>
       <c r="O55" t="s">
         <v>29</v>
       </c>
-      <c r="P55">
-        <v>2050</v>
+      <c r="P55" t="s">
+        <v>114</v>
       </c>
       <c r="Q55" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="R55" t="s">
-        <v>23</v>
-      </c>
-      <c r="S55" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S55" s="1">
+        <v>44308.04166666667</v>
       </c>
       <c r="T55" t="s">
         <v>32</v>
@@ -5118,15 +5663,15 @@
         <v>23</v>
       </c>
       <c r="V55" s="1">
-        <v>45771.04166666667</v>
+        <v>45414.04166666667</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>40004338</v>
+        <v>40035712</v>
       </c>
       <c r="B56" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C56" t="s">
         <v>23</v>
@@ -5138,81 +5683,81 @@
         <v>25</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H56" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I56" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J56" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K56" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L56" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P56" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="Q56" t="s">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="R56" t="s">
-        <v>76</v>
-      </c>
-      <c r="S56" s="1">
-        <v>44490.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S56" t="s">
+        <v>23</v>
       </c>
       <c r="T56" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U56" t="s">
         <v>23</v>
       </c>
       <c r="V56" s="1">
-        <v>45036.04166666667</v>
+        <v>46149.04166666667</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>40021569</v>
+        <v>40012677</v>
       </c>
       <c r="B57" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>251</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G57" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H57" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="I57" t="s">
         <v>29</v>
@@ -5221,31 +5766,31 @@
         <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="O57" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P57" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="Q57" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="R57" t="s">
-        <v>23</v>
-      </c>
-      <c r="S57" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S57" s="1">
+        <v>44308.04166666667</v>
       </c>
       <c r="T57" t="s">
         <v>32</v>
@@ -5254,33 +5799,33 @@
         <v>23</v>
       </c>
       <c r="V57" s="1">
-        <v>45792.04166666667</v>
+        <v>46044.04166666667</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>40003483</v>
+        <v>40005313</v>
       </c>
       <c r="B58" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H58" t="s">
-        <v>238</v>
+        <v>43</v>
       </c>
       <c r="I58" t="s">
         <v>29</v>
@@ -5289,7 +5834,7 @@
         <v>30</v>
       </c>
       <c r="K58">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="L58" t="s">
         <v>23</v>
@@ -5307,7 +5852,7 @@
         <v>23</v>
       </c>
       <c r="Q58" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="R58" t="s">
         <v>23</v>
@@ -5322,15 +5867,15 @@
         <v>23</v>
       </c>
       <c r="V58" s="1">
-        <v>46037.04166666667</v>
+        <v>45400.04166666667</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>40024642</v>
+        <v>40008934</v>
       </c>
       <c r="B59" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
@@ -5339,16 +5884,16 @@
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="H59" t="s">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="I59" t="s">
         <v>29</v>
@@ -5375,7 +5920,7 @@
         <v>23</v>
       </c>
       <c r="Q59" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="R59" t="s">
         <v>23</v>
@@ -5390,15 +5935,15 @@
         <v>23</v>
       </c>
       <c r="V59" s="1">
-        <v>45953.04166666667</v>
+        <v>45603.04166666667</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>40020897</v>
+        <v>40000725</v>
       </c>
       <c r="B60" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C60" t="s">
         <v>23</v>
@@ -5410,16 +5955,16 @@
         <v>25</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H60" t="s">
-        <v>246</v>
+        <v>67</v>
       </c>
       <c r="I60" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J60" t="s">
         <v>23</v>
@@ -5437,7 +5982,7 @@
         <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P60" t="s">
         <v>23</v>
@@ -5455,18 +6000,18 @@
         <v>23</v>
       </c>
       <c r="U60" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="V60" s="1">
-        <v>46037.04166666667</v>
+        <v>45225.04166666667</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>40017861</v>
+        <v>40025116</v>
       </c>
       <c r="B61" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -5475,25 +6020,25 @@
         <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="I61" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J61" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K61" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="L61" t="s">
         <v>23</v>
@@ -5505,13 +6050,13 @@
         <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="P61" t="s">
         <v>23</v>
       </c>
       <c r="Q61" t="s">
-        <v>248</v>
+        <v>23</v>
       </c>
       <c r="R61" t="s">
         <v>23</v>
@@ -5520,39 +6065,39 @@
         <v>23</v>
       </c>
       <c r="T61" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U61" t="s">
         <v>23</v>
       </c>
       <c r="V61" s="1">
-        <v>45862.04166666667</v>
+        <v>45890.04166666667</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>40001042</v>
+        <v>40007418</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C62" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D62" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="G62" t="s">
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>252</v>
+        <v>137</v>
       </c>
       <c r="I62" t="s">
         <v>29</v>
@@ -5579,13 +6124,13 @@
         <v>2050</v>
       </c>
       <c r="Q62" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="R62" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="S62" s="1">
-        <v>43709.04166666667</v>
+        <v>43952.04166666667</v>
       </c>
       <c r="T62" t="s">
         <v>32</v>
@@ -5594,15 +6139,15 @@
         <v>23</v>
       </c>
       <c r="V62" s="1">
-        <v>44805.04166666667</v>
+        <v>45414.04166666667</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>40000344</v>
+        <v>40002197</v>
       </c>
       <c r="B63" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -5611,16 +6156,16 @@
         <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G63" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="I63" t="s">
         <v>29</v>
@@ -5647,7 +6192,7 @@
         <v>23</v>
       </c>
       <c r="Q63" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="R63" t="s">
         <v>23</v>
@@ -5662,83 +6207,83 @@
         <v>23</v>
       </c>
       <c r="V63" s="1">
-        <v>45533.04166666667</v>
+        <v>45407.04166666667</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>40010080</v>
+        <v>40005117</v>
       </c>
       <c r="B64" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>270</v>
       </c>
       <c r="E64" t="s">
         <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="G64" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H64" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="I64" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J64" t="s">
-        <v>23</v>
-      </c>
-      <c r="K64" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="K64">
+        <v>2030</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M64" t="s">
-        <v>23</v>
-      </c>
-      <c r="N64" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N64">
+        <v>2050</v>
       </c>
       <c r="O64" t="s">
-        <v>44</v>
-      </c>
-      <c r="P64" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P64">
+        <v>2050</v>
       </c>
       <c r="Q64" t="s">
-        <v>23</v>
+        <v>271</v>
       </c>
       <c r="R64" t="s">
-        <v>23</v>
-      </c>
-      <c r="S64" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S64" s="1">
+        <v>44000.04166666667</v>
       </c>
       <c r="T64" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U64" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="V64" s="1">
-        <v>45554.04166666667</v>
+        <v>45841.04166666667</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>40031412</v>
+        <v>40015696</v>
       </c>
       <c r="B65" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
@@ -5747,16 +6292,16 @@
         <v>23</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="G65" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="H65" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="I65" t="s">
         <v>29</v>
@@ -5764,8 +6309,8 @@
       <c r="J65" t="s">
         <v>30</v>
       </c>
-      <c r="K65" t="s">
-        <v>50</v>
+      <c r="K65">
+        <v>2030</v>
       </c>
       <c r="L65" t="s">
         <v>23</v>
@@ -5783,7 +6328,7 @@
         <v>23</v>
       </c>
       <c r="Q65" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="R65" t="s">
         <v>23</v>
@@ -5798,33 +6343,33 @@
         <v>23</v>
       </c>
       <c r="V65" s="1">
-        <v>46086.04166666667</v>
+        <v>44714.04166666667</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>40032853</v>
+        <v>40006743</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>275</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>276</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F66" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H66" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="I66" t="s">
         <v>29</v>
@@ -5833,31 +6378,31 @@
         <v>30</v>
       </c>
       <c r="K66">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
-      </c>
-      <c r="N66" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N66">
+        <v>2050</v>
       </c>
       <c r="O66" t="s">
-        <v>23</v>
-      </c>
-      <c r="P66" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P66">
+        <v>2050</v>
       </c>
       <c r="Q66" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="R66" t="s">
-        <v>23</v>
-      </c>
-      <c r="S66" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S66" s="1">
+        <v>44476.04166666667</v>
       </c>
       <c r="T66" t="s">
         <v>32</v>
@@ -5866,33 +6411,33 @@
         <v>23</v>
       </c>
       <c r="V66" s="1">
-        <v>46156.04166666667</v>
+        <v>45267.04166666667</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>40001097</v>
+        <v>40006376</v>
       </c>
       <c r="B67" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C67" t="s">
-        <v>262</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>263</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>25</v>
       </c>
       <c r="F67" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H67" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
         <v>29</v>
@@ -5901,7 +6446,7 @@
         <v>30</v>
       </c>
       <c r="K67">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="L67" t="s">
         <v>23</v>
@@ -5913,54 +6458,54 @@
         <v>23</v>
       </c>
       <c r="O67" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P67" t="s">
         <v>23</v>
       </c>
       <c r="Q67" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="R67" t="s">
-        <v>23</v>
-      </c>
-      <c r="S67" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S67" s="1">
+        <v>44707.04166666667</v>
       </c>
       <c r="T67" t="s">
         <v>32</v>
       </c>
       <c r="U67" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="V67" s="1">
-        <v>44644.04166666667</v>
+        <v>45666.04166666667</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>40010293</v>
+        <v>40007935</v>
       </c>
       <c r="B68" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>268</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F68" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="I68" t="s">
         <v>29</v>
@@ -5969,7 +6514,7 @@
         <v>30</v>
       </c>
       <c r="K68">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="L68" t="s">
         <v>29</v>
@@ -5978,39 +6523,39 @@
         <v>30</v>
       </c>
       <c r="N68">
-        <v>2050</v>
+        <v>2035</v>
       </c>
       <c r="O68" t="s">
         <v>29</v>
       </c>
       <c r="P68">
-        <v>2050</v>
+        <v>2035</v>
       </c>
       <c r="Q68" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="R68" t="s">
-        <v>76</v>
-      </c>
-      <c r="S68" s="1">
-        <v>44462.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S68" t="s">
+        <v>23</v>
       </c>
       <c r="T68" t="s">
         <v>32</v>
       </c>
       <c r="U68" t="s">
-        <v>270</v>
+        <v>23</v>
       </c>
       <c r="V68" s="1">
-        <v>45771.04166666667</v>
+        <v>45057.04166666667</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>40002060</v>
+        <v>40019154</v>
       </c>
       <c r="B69" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -6019,16 +6564,16 @@
         <v>23</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G69" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="H69" t="s">
-        <v>64</v>
+        <v>267</v>
       </c>
       <c r="I69" t="s">
         <v>29</v>
@@ -6037,7 +6582,7 @@
         <v>30</v>
       </c>
       <c r="K69">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="L69" t="s">
         <v>23</v>
@@ -6055,13 +6600,13 @@
         <v>23</v>
       </c>
       <c r="Q69" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="R69" t="s">
-        <v>76</v>
-      </c>
-      <c r="S69" s="1">
-        <v>44020.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S69" t="s">
+        <v>23</v>
       </c>
       <c r="T69" t="s">
         <v>32</v>
@@ -6070,33 +6615,33 @@
         <v>23</v>
       </c>
       <c r="V69" s="1">
-        <v>45834.04166666667</v>
+        <v>45764.04166666667</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>40007117</v>
+        <v>40009928</v>
       </c>
       <c r="B70" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>288</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>289</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F70" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G70" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I70" t="s">
         <v>29</v>
@@ -6114,22 +6659,22 @@
         <v>30</v>
       </c>
       <c r="N70">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="O70" t="s">
         <v>29</v>
       </c>
       <c r="P70">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="Q70" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="R70" t="s">
-        <v>23</v>
-      </c>
-      <c r="S70" t="s">
-        <v>23</v>
+        <v>71</v>
+      </c>
+      <c r="S70" s="1">
+        <v>43709.04166666667</v>
       </c>
       <c r="T70" t="s">
         <v>32</v>
@@ -6138,15 +6683,15 @@
         <v>23</v>
       </c>
       <c r="V70" s="1">
-        <v>45113.04166666667</v>
+        <v>45267.04166666667</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>40018805</v>
+        <v>40011125</v>
       </c>
       <c r="B71" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -6158,13 +6703,13 @@
         <v>25</v>
       </c>
       <c r="F71" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="G71" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>277</v>
+        <v>67</v>
       </c>
       <c r="I71" t="s">
         <v>29</v>
@@ -6176,22 +6721,22 @@
         <v>2030</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M71" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="N71">
+        <v>2050</v>
       </c>
       <c r="O71" t="s">
-        <v>23</v>
-      </c>
-      <c r="P71" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="P71">
+        <v>2050</v>
       </c>
       <c r="Q71" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="R71" t="s">
         <v>23</v>
@@ -6206,42 +6751,42 @@
         <v>23</v>
       </c>
       <c r="V71" s="1">
-        <v>45848.04166666667</v>
+        <v>45484.04166666667</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>40016031</v>
+        <v>40024906</v>
       </c>
       <c r="B72" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>294</v>
       </c>
       <c r="E72" t="s">
         <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>280</v>
+        <v>42</v>
       </c>
       <c r="G72" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="I72" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J72" t="s">
-        <v>30</v>
-      </c>
-      <c r="K72">
-        <v>2030</v>
+        <v>23</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
       </c>
       <c r="L72" t="s">
         <v>23</v>
@@ -6253,13 +6798,13 @@
         <v>23</v>
       </c>
       <c r="O72" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P72" t="s">
         <v>23</v>
       </c>
       <c r="Q72" t="s">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="R72" t="s">
         <v>23</v>
@@ -6268,39 +6813,39 @@
         <v>23</v>
       </c>
       <c r="T72" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U72" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V72" s="1">
-        <v>45904.04166666667</v>
+        <v>45960.04166666667</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>40008764</v>
+        <v>40004519</v>
       </c>
       <c r="B73" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C73" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D73" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="G73" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="H73" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="I73" t="s">
         <v>29</v>
@@ -6309,7 +6854,7 @@
         <v>30</v>
       </c>
       <c r="K73" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L73" t="s">
         <v>23</v>
@@ -6321,54 +6866,54 @@
         <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="P73" t="s">
         <v>23</v>
       </c>
       <c r="Q73" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="R73" t="s">
-        <v>76</v>
-      </c>
-      <c r="S73" s="1">
-        <v>43647.04166666667</v>
+        <v>23</v>
+      </c>
+      <c r="S73" t="s">
+        <v>23</v>
       </c>
       <c r="T73" t="s">
         <v>32</v>
       </c>
       <c r="U73" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="V73" s="1">
-        <v>45407.04166666667</v>
+        <v>46282.04166666667</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>40027334</v>
+        <v>40009717</v>
       </c>
       <c r="B74" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="G74" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H74" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
       <c r="I74" t="s">
         <v>29</v>
@@ -6377,7 +6922,7 @@
         <v>30</v>
       </c>
       <c r="K74">
-        <v>2035</v>
+        <v>2026</v>
       </c>
       <c r="L74" t="s">
         <v>23</v>
@@ -6395,7 +6940,7 @@
         <v>23</v>
       </c>
       <c r="Q74" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="R74" t="s">
         <v>23</v>
@@ -6410,7 +6955,2523 @@
         <v>23</v>
       </c>
       <c r="V74" s="1">
-        <v>46240.04166666667</v>
+        <v>44203.04166666667</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>40001722</v>
+      </c>
+      <c r="B75" t="s">
+        <v>303</v>
+      </c>
+      <c r="C75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D75" t="s">
+        <v>305</v>
+      </c>
+      <c r="E75" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" t="s">
+        <v>306</v>
+      </c>
+      <c r="G75" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" t="s">
+        <v>61</v>
+      </c>
+      <c r="I75" t="s">
+        <v>29</v>
+      </c>
+      <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75">
+        <v>2030</v>
+      </c>
+      <c r="L75" t="s">
+        <v>29</v>
+      </c>
+      <c r="M75" t="s">
+        <v>30</v>
+      </c>
+      <c r="N75">
+        <v>2040</v>
+      </c>
+      <c r="O75" t="s">
+        <v>29</v>
+      </c>
+      <c r="P75">
+        <v>2040</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>307</v>
+      </c>
+      <c r="R75" t="s">
+        <v>71</v>
+      </c>
+      <c r="S75" s="1">
+        <v>43709.04166666667</v>
+      </c>
+      <c r="T75" t="s">
+        <v>32</v>
+      </c>
+      <c r="U75" t="s">
+        <v>23</v>
+      </c>
+      <c r="V75" s="1">
+        <v>45708.04166666667</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>40011759</v>
+      </c>
+      <c r="B76" t="s">
+        <v>308</v>
+      </c>
+      <c r="C76" t="s">
+        <v>309</v>
+      </c>
+      <c r="D76" t="s">
+        <v>310</v>
+      </c>
+      <c r="E76" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" t="s">
+        <v>65</v>
+      </c>
+      <c r="G76" t="s">
+        <v>66</v>
+      </c>
+      <c r="H76" t="s">
+        <v>155</v>
+      </c>
+      <c r="I76" t="s">
+        <v>29</v>
+      </c>
+      <c r="J76" t="s">
+        <v>30</v>
+      </c>
+      <c r="K76">
+        <v>2033</v>
+      </c>
+      <c r="L76" t="s">
+        <v>29</v>
+      </c>
+      <c r="M76" t="s">
+        <v>30</v>
+      </c>
+      <c r="N76">
+        <v>2045</v>
+      </c>
+      <c r="O76" t="s">
+        <v>29</v>
+      </c>
+      <c r="P76">
+        <v>2045</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>311</v>
+      </c>
+      <c r="R76" t="s">
+        <v>71</v>
+      </c>
+      <c r="S76" s="1">
+        <v>44448.04166666667</v>
+      </c>
+      <c r="T76" t="s">
+        <v>32</v>
+      </c>
+      <c r="U76" t="s">
+        <v>23</v>
+      </c>
+      <c r="V76" s="1">
+        <v>45764.04166666667</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>40012183</v>
+      </c>
+      <c r="B77" t="s">
+        <v>312</v>
+      </c>
+      <c r="C77" t="s">
+        <v>313</v>
+      </c>
+      <c r="D77" t="s">
+        <v>314</v>
+      </c>
+      <c r="E77" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" t="s">
+        <v>65</v>
+      </c>
+      <c r="G77" t="s">
+        <v>66</v>
+      </c>
+      <c r="H77" t="s">
+        <v>247</v>
+      </c>
+      <c r="I77" t="s">
+        <v>29</v>
+      </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77">
+        <v>2030</v>
+      </c>
+      <c r="L77" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" t="s">
+        <v>30</v>
+      </c>
+      <c r="N77">
+        <v>2050</v>
+      </c>
+      <c r="O77" t="s">
+        <v>29</v>
+      </c>
+      <c r="P77">
+        <v>2050</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>315</v>
+      </c>
+      <c r="R77" t="s">
+        <v>71</v>
+      </c>
+      <c r="S77" s="1">
+        <v>43647.04166666667</v>
+      </c>
+      <c r="T77" t="s">
+        <v>32</v>
+      </c>
+      <c r="U77" t="s">
+        <v>23</v>
+      </c>
+      <c r="V77" s="1">
+        <v>44875.04166666667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>40011442</v>
+      </c>
+      <c r="B78" t="s">
+        <v>316</v>
+      </c>
+      <c r="C78" t="s">
+        <v>317</v>
+      </c>
+      <c r="D78" t="s">
+        <v>318</v>
+      </c>
+      <c r="E78" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" t="s">
+        <v>83</v>
+      </c>
+      <c r="G78" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" t="s">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" t="s">
+        <v>30</v>
+      </c>
+      <c r="K78">
+        <v>2030</v>
+      </c>
+      <c r="L78" t="s">
+        <v>29</v>
+      </c>
+      <c r="M78" t="s">
+        <v>30</v>
+      </c>
+      <c r="N78">
+        <v>2050</v>
+      </c>
+      <c r="O78" t="s">
+        <v>29</v>
+      </c>
+      <c r="P78">
+        <v>2050</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>319</v>
+      </c>
+      <c r="R78" t="s">
+        <v>23</v>
+      </c>
+      <c r="S78" t="s">
+        <v>23</v>
+      </c>
+      <c r="T78" t="s">
+        <v>32</v>
+      </c>
+      <c r="U78" t="s">
+        <v>23</v>
+      </c>
+      <c r="V78" s="1">
+        <v>45771.04166666667</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>40004338</v>
+      </c>
+      <c r="B79" t="s">
+        <v>320</v>
+      </c>
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" t="s">
+        <v>37</v>
+      </c>
+      <c r="H79" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" t="s">
+        <v>29</v>
+      </c>
+      <c r="J79" t="s">
+        <v>30</v>
+      </c>
+      <c r="K79" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" t="s">
+        <v>29</v>
+      </c>
+      <c r="M79" t="s">
+        <v>30</v>
+      </c>
+      <c r="N79" t="s">
+        <v>114</v>
+      </c>
+      <c r="O79" t="s">
+        <v>29</v>
+      </c>
+      <c r="P79" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>321</v>
+      </c>
+      <c r="R79" t="s">
+        <v>71</v>
+      </c>
+      <c r="S79" s="1">
+        <v>44490.04166666667</v>
+      </c>
+      <c r="T79" t="s">
+        <v>32</v>
+      </c>
+      <c r="U79" t="s">
+        <v>23</v>
+      </c>
+      <c r="V79" s="1">
+        <v>45036.04166666667</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>40010750</v>
+      </c>
+      <c r="B80" t="s">
+        <v>322</v>
+      </c>
+      <c r="C80" t="s">
+        <v>323</v>
+      </c>
+      <c r="D80" t="s">
+        <v>324</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" t="s">
+        <v>37</v>
+      </c>
+      <c r="H80" t="s">
+        <v>67</v>
+      </c>
+      <c r="I80" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80">
+        <v>2030</v>
+      </c>
+      <c r="L80" t="s">
+        <v>29</v>
+      </c>
+      <c r="M80" t="s">
+        <v>30</v>
+      </c>
+      <c r="N80">
+        <v>2050</v>
+      </c>
+      <c r="O80" t="s">
+        <v>29</v>
+      </c>
+      <c r="P80">
+        <v>2050</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>325</v>
+      </c>
+      <c r="R80" t="s">
+        <v>71</v>
+      </c>
+      <c r="S80" s="1">
+        <v>43922.04166666667</v>
+      </c>
+      <c r="T80" t="s">
+        <v>32</v>
+      </c>
+      <c r="U80" t="s">
+        <v>23</v>
+      </c>
+      <c r="V80" s="1">
+        <v>45806.04166666667</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>40017172</v>
+      </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" t="s">
+        <v>98</v>
+      </c>
+      <c r="G81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" t="s">
+        <v>261</v>
+      </c>
+      <c r="I81" t="s">
+        <v>47</v>
+      </c>
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" t="s">
+        <v>23</v>
+      </c>
+      <c r="O81" t="s">
+        <v>23</v>
+      </c>
+      <c r="P81" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>23</v>
+      </c>
+      <c r="R81" t="s">
+        <v>23</v>
+      </c>
+      <c r="S81" t="s">
+        <v>23</v>
+      </c>
+      <c r="T81" t="s">
+        <v>23</v>
+      </c>
+      <c r="U81" t="s">
+        <v>23</v>
+      </c>
+      <c r="V81" s="1">
+        <v>45638.04166666667</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>40004202</v>
+      </c>
+      <c r="B82" t="s">
+        <v>327</v>
+      </c>
+      <c r="C82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82" t="s">
+        <v>37</v>
+      </c>
+      <c r="H82" t="s">
+        <v>200</v>
+      </c>
+      <c r="I82" t="s">
+        <v>29</v>
+      </c>
+      <c r="J82" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82">
+        <v>2030</v>
+      </c>
+      <c r="L82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" t="s">
+        <v>23</v>
+      </c>
+      <c r="O82" t="s">
+        <v>23</v>
+      </c>
+      <c r="P82" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>328</v>
+      </c>
+      <c r="R82" t="s">
+        <v>23</v>
+      </c>
+      <c r="S82" t="s">
+        <v>23</v>
+      </c>
+      <c r="T82" t="s">
+        <v>32</v>
+      </c>
+      <c r="U82" t="s">
+        <v>23</v>
+      </c>
+      <c r="V82" s="1">
+        <v>45211.04166666667</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>40003236</v>
+      </c>
+      <c r="B83" t="s">
+        <v>329</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>330</v>
+      </c>
+      <c r="E83" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" t="s">
+        <v>259</v>
+      </c>
+      <c r="G83" t="s">
+        <v>66</v>
+      </c>
+      <c r="H83" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" t="s">
+        <v>29</v>
+      </c>
+      <c r="J83" t="s">
+        <v>30</v>
+      </c>
+      <c r="K83">
+        <v>2030</v>
+      </c>
+      <c r="L83" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" t="s">
+        <v>23</v>
+      </c>
+      <c r="O83" t="s">
+        <v>23</v>
+      </c>
+      <c r="P83" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>331</v>
+      </c>
+      <c r="R83" t="s">
+        <v>71</v>
+      </c>
+      <c r="S83" s="1">
+        <v>44301.04166666667</v>
+      </c>
+      <c r="T83" t="s">
+        <v>32</v>
+      </c>
+      <c r="U83" t="s">
+        <v>23</v>
+      </c>
+      <c r="V83" s="1">
+        <v>45183.04166666667</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>40035096</v>
+      </c>
+      <c r="B84" t="s">
+        <v>332</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>333</v>
+      </c>
+      <c r="E84" t="s">
+        <v>49</v>
+      </c>
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" t="s">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" t="s">
+        <v>30</v>
+      </c>
+      <c r="K84">
+        <v>2034</v>
+      </c>
+      <c r="L84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" t="s">
+        <v>23</v>
+      </c>
+      <c r="P84" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>334</v>
+      </c>
+      <c r="R84" t="s">
+        <v>23</v>
+      </c>
+      <c r="S84" t="s">
+        <v>23</v>
+      </c>
+      <c r="T84" t="s">
+        <v>32</v>
+      </c>
+      <c r="U84" t="s">
+        <v>23</v>
+      </c>
+      <c r="V84" s="1">
+        <v>46191.04166666667</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>40000209</v>
+      </c>
+      <c r="B85" t="s">
+        <v>335</v>
+      </c>
+      <c r="C85" t="s">
+        <v>336</v>
+      </c>
+      <c r="D85" t="s">
+        <v>337</v>
+      </c>
+      <c r="E85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" t="s">
+        <v>29</v>
+      </c>
+      <c r="J85" t="s">
+        <v>30</v>
+      </c>
+      <c r="K85">
+        <v>2030</v>
+      </c>
+      <c r="L85" t="s">
+        <v>23</v>
+      </c>
+      <c r="M85" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" t="s">
+        <v>23</v>
+      </c>
+      <c r="O85" t="s">
+        <v>23</v>
+      </c>
+      <c r="P85" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>338</v>
+      </c>
+      <c r="R85" t="s">
+        <v>23</v>
+      </c>
+      <c r="S85" t="s">
+        <v>23</v>
+      </c>
+      <c r="T85" t="s">
+        <v>32</v>
+      </c>
+      <c r="U85" t="s">
+        <v>23</v>
+      </c>
+      <c r="V85" s="1">
+        <v>45274.04166666667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>40020897</v>
+      </c>
+      <c r="B86" t="s">
+        <v>339</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" t="s">
+        <v>280</v>
+      </c>
+      <c r="G86" t="s">
+        <v>66</v>
+      </c>
+      <c r="H86" t="s">
+        <v>340</v>
+      </c>
+      <c r="I86" t="s">
+        <v>47</v>
+      </c>
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>23</v>
+      </c>
+      <c r="M86" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" t="s">
+        <v>23</v>
+      </c>
+      <c r="O86" t="s">
+        <v>23</v>
+      </c>
+      <c r="P86" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>23</v>
+      </c>
+      <c r="R86" t="s">
+        <v>23</v>
+      </c>
+      <c r="S86" t="s">
+        <v>23</v>
+      </c>
+      <c r="T86" t="s">
+        <v>23</v>
+      </c>
+      <c r="U86" t="s">
+        <v>23</v>
+      </c>
+      <c r="V86" s="1">
+        <v>46037.04166666667</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>40017861</v>
+      </c>
+      <c r="B87" t="s">
+        <v>341</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" t="s">
+        <v>49</v>
+      </c>
+      <c r="F87" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" t="s">
+        <v>66</v>
+      </c>
+      <c r="H87" t="s">
+        <v>200</v>
+      </c>
+      <c r="I87" t="s">
+        <v>29</v>
+      </c>
+      <c r="J87" t="s">
+        <v>30</v>
+      </c>
+      <c r="K87" t="s">
+        <v>53</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" t="s">
+        <v>23</v>
+      </c>
+      <c r="O87" t="s">
+        <v>23</v>
+      </c>
+      <c r="P87" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>342</v>
+      </c>
+      <c r="R87" t="s">
+        <v>23</v>
+      </c>
+      <c r="S87" t="s">
+        <v>23</v>
+      </c>
+      <c r="T87" t="s">
+        <v>32</v>
+      </c>
+      <c r="U87" t="s">
+        <v>23</v>
+      </c>
+      <c r="V87" s="1">
+        <v>45862.04166666667</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>40015160</v>
+      </c>
+      <c r="B88" t="s">
+        <v>343</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
+        <v>344</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>345</v>
+      </c>
+      <c r="G88" t="s">
+        <v>346</v>
+      </c>
+      <c r="H88" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" t="s">
+        <v>29</v>
+      </c>
+      <c r="J88" t="s">
+        <v>30</v>
+      </c>
+      <c r="K88">
+        <v>2030</v>
+      </c>
+      <c r="L88" t="s">
+        <v>29</v>
+      </c>
+      <c r="M88" t="s">
+        <v>30</v>
+      </c>
+      <c r="N88">
+        <v>2050</v>
+      </c>
+      <c r="O88" t="s">
+        <v>29</v>
+      </c>
+      <c r="P88">
+        <v>2050</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>347</v>
+      </c>
+      <c r="R88" t="s">
+        <v>23</v>
+      </c>
+      <c r="S88" t="s">
+        <v>23</v>
+      </c>
+      <c r="T88" t="s">
+        <v>32</v>
+      </c>
+      <c r="U88" t="s">
+        <v>23</v>
+      </c>
+      <c r="V88" s="1">
+        <v>45799.04166666667</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>40035020</v>
+      </c>
+      <c r="B89" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" t="s">
+        <v>349</v>
+      </c>
+      <c r="E89" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" t="s">
+        <v>218</v>
+      </c>
+      <c r="G89" t="s">
+        <v>219</v>
+      </c>
+      <c r="H89" t="s">
+        <v>247</v>
+      </c>
+      <c r="I89" t="s">
+        <v>29</v>
+      </c>
+      <c r="J89" t="s">
+        <v>30</v>
+      </c>
+      <c r="K89" t="s">
+        <v>350</v>
+      </c>
+      <c r="L89" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" t="s">
+        <v>23</v>
+      </c>
+      <c r="O89" t="s">
+        <v>23</v>
+      </c>
+      <c r="P89" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>351</v>
+      </c>
+      <c r="R89" t="s">
+        <v>23</v>
+      </c>
+      <c r="S89" t="s">
+        <v>23</v>
+      </c>
+      <c r="T89" t="s">
+        <v>32</v>
+      </c>
+      <c r="U89" t="s">
+        <v>23</v>
+      </c>
+      <c r="V89" s="1">
+        <v>46198.04166666667</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>40012397</v>
+      </c>
+      <c r="B90" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" t="s">
+        <v>354</v>
+      </c>
+      <c r="E90" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" t="s">
+        <v>141</v>
+      </c>
+      <c r="G90" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" t="s">
+        <v>137</v>
+      </c>
+      <c r="I90" t="s">
+        <v>29</v>
+      </c>
+      <c r="J90" t="s">
+        <v>30</v>
+      </c>
+      <c r="K90">
+        <v>2030</v>
+      </c>
+      <c r="L90" t="s">
+        <v>29</v>
+      </c>
+      <c r="M90" t="s">
+        <v>30</v>
+      </c>
+      <c r="N90">
+        <v>2050</v>
+      </c>
+      <c r="O90" t="s">
+        <v>29</v>
+      </c>
+      <c r="P90">
+        <v>2050</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>355</v>
+      </c>
+      <c r="R90" t="s">
+        <v>71</v>
+      </c>
+      <c r="S90" s="1">
+        <v>43647.04166666667</v>
+      </c>
+      <c r="T90" t="s">
+        <v>32</v>
+      </c>
+      <c r="U90" t="s">
+        <v>23</v>
+      </c>
+      <c r="V90" s="1">
+        <v>44798.04166666667</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>40014131</v>
+      </c>
+      <c r="B91" t="s">
+        <v>356</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" t="s">
+        <v>29</v>
+      </c>
+      <c r="J91" t="s">
+        <v>30</v>
+      </c>
+      <c r="K91" t="s">
+        <v>357</v>
+      </c>
+      <c r="L91" t="s">
+        <v>29</v>
+      </c>
+      <c r="M91" t="s">
+        <v>30</v>
+      </c>
+      <c r="N91" t="s">
+        <v>80</v>
+      </c>
+      <c r="O91" t="s">
+        <v>29</v>
+      </c>
+      <c r="P91" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>358</v>
+      </c>
+      <c r="R91" t="s">
+        <v>23</v>
+      </c>
+      <c r="S91" t="s">
+        <v>23</v>
+      </c>
+      <c r="T91" t="s">
+        <v>32</v>
+      </c>
+      <c r="U91" t="s">
+        <v>23</v>
+      </c>
+      <c r="V91" s="1">
+        <v>45988.04166666667</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>40016644</v>
+      </c>
+      <c r="B92" t="s">
+        <v>359</v>
+      </c>
+      <c r="C92" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" t="s">
+        <v>50</v>
+      </c>
+      <c r="G92" t="s">
+        <v>51</v>
+      </c>
+      <c r="H92" t="s">
+        <v>137</v>
+      </c>
+      <c r="I92" t="s">
+        <v>29</v>
+      </c>
+      <c r="J92" t="s">
+        <v>30</v>
+      </c>
+      <c r="K92">
+        <v>2030</v>
+      </c>
+      <c r="L92" t="s">
+        <v>23</v>
+      </c>
+      <c r="M92" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" t="s">
+        <v>23</v>
+      </c>
+      <c r="O92" t="s">
+        <v>23</v>
+      </c>
+      <c r="P92" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>360</v>
+      </c>
+      <c r="R92" t="s">
+        <v>23</v>
+      </c>
+      <c r="S92" t="s">
+        <v>23</v>
+      </c>
+      <c r="T92" t="s">
+        <v>32</v>
+      </c>
+      <c r="U92" t="s">
+        <v>23</v>
+      </c>
+      <c r="V92" s="1">
+        <v>45624.04166666667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>40010080</v>
+      </c>
+      <c r="B93" t="s">
+        <v>361</v>
+      </c>
+      <c r="C93" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" t="s">
+        <v>60</v>
+      </c>
+      <c r="G93" t="s">
+        <v>51</v>
+      </c>
+      <c r="H93" t="s">
+        <v>61</v>
+      </c>
+      <c r="I93" t="s">
+        <v>47</v>
+      </c>
+      <c r="J93" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" t="s">
+        <v>23</v>
+      </c>
+      <c r="O93" t="s">
+        <v>47</v>
+      </c>
+      <c r="P93" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>23</v>
+      </c>
+      <c r="R93" t="s">
+        <v>23</v>
+      </c>
+      <c r="S93" t="s">
+        <v>23</v>
+      </c>
+      <c r="T93" t="s">
+        <v>23</v>
+      </c>
+      <c r="U93" t="s">
+        <v>23</v>
+      </c>
+      <c r="V93" s="1">
+        <v>45554.04166666667</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>40031412</v>
+      </c>
+      <c r="B94" t="s">
+        <v>362</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" t="s">
+        <v>49</v>
+      </c>
+      <c r="F94" t="s">
+        <v>50</v>
+      </c>
+      <c r="G94" t="s">
+        <v>51</v>
+      </c>
+      <c r="H94" t="s">
+        <v>363</v>
+      </c>
+      <c r="I94" t="s">
+        <v>29</v>
+      </c>
+      <c r="J94" t="s">
+        <v>30</v>
+      </c>
+      <c r="K94" t="s">
+        <v>53</v>
+      </c>
+      <c r="L94" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" t="s">
+        <v>23</v>
+      </c>
+      <c r="O94" t="s">
+        <v>23</v>
+      </c>
+      <c r="P94" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>364</v>
+      </c>
+      <c r="R94" t="s">
+        <v>23</v>
+      </c>
+      <c r="S94" t="s">
+        <v>23</v>
+      </c>
+      <c r="T94" t="s">
+        <v>32</v>
+      </c>
+      <c r="U94" t="s">
+        <v>23</v>
+      </c>
+      <c r="V94" s="1">
+        <v>46086.04166666667</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>40003681</v>
+      </c>
+      <c r="B95" t="s">
+        <v>365</v>
+      </c>
+      <c r="C95" t="s">
+        <v>366</v>
+      </c>
+      <c r="D95" t="s">
+        <v>367</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>42</v>
+      </c>
+      <c r="G95" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" t="s">
+        <v>137</v>
+      </c>
+      <c r="I95" t="s">
+        <v>29</v>
+      </c>
+      <c r="J95" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95" t="s">
+        <v>53</v>
+      </c>
+      <c r="L95" t="s">
+        <v>29</v>
+      </c>
+      <c r="M95" t="s">
+        <v>30</v>
+      </c>
+      <c r="N95" t="s">
+        <v>80</v>
+      </c>
+      <c r="O95" t="s">
+        <v>29</v>
+      </c>
+      <c r="P95" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>368</v>
+      </c>
+      <c r="R95" t="s">
+        <v>71</v>
+      </c>
+      <c r="S95" s="1">
+        <v>44427.04166666667</v>
+      </c>
+      <c r="T95" t="s">
+        <v>32</v>
+      </c>
+      <c r="U95" t="s">
+        <v>23</v>
+      </c>
+      <c r="V95" s="1">
+        <v>45554.04166666667</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>40005863</v>
+      </c>
+      <c r="B96" t="s">
+        <v>369</v>
+      </c>
+      <c r="C96" t="s">
+        <v>370</v>
+      </c>
+      <c r="D96" t="s">
+        <v>371</v>
+      </c>
+      <c r="E96" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" t="s">
+        <v>42</v>
+      </c>
+      <c r="G96" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" t="s">
+        <v>137</v>
+      </c>
+      <c r="I96" t="s">
+        <v>29</v>
+      </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96">
+        <v>2030</v>
+      </c>
+      <c r="L96" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" t="s">
+        <v>23</v>
+      </c>
+      <c r="N96" t="s">
+        <v>23</v>
+      </c>
+      <c r="O96" t="s">
+        <v>23</v>
+      </c>
+      <c r="P96" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>372</v>
+      </c>
+      <c r="R96" t="s">
+        <v>23</v>
+      </c>
+      <c r="S96" t="s">
+        <v>23</v>
+      </c>
+      <c r="T96" t="s">
+        <v>32</v>
+      </c>
+      <c r="U96" t="s">
+        <v>23</v>
+      </c>
+      <c r="V96" s="1">
+        <v>44308.04166666667</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>40015849</v>
+      </c>
+      <c r="B97" t="s">
+        <v>373</v>
+      </c>
+      <c r="C97" t="s">
+        <v>374</v>
+      </c>
+      <c r="D97" t="s">
+        <v>375</v>
+      </c>
+      <c r="E97" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" t="s">
+        <v>209</v>
+      </c>
+      <c r="G97" t="s">
+        <v>134</v>
+      </c>
+      <c r="H97" t="s">
+        <v>210</v>
+      </c>
+      <c r="I97" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" t="s">
+        <v>30</v>
+      </c>
+      <c r="K97">
+        <v>2025</v>
+      </c>
+      <c r="L97" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" t="s">
+        <v>23</v>
+      </c>
+      <c r="O97" t="s">
+        <v>39</v>
+      </c>
+      <c r="P97" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>376</v>
+      </c>
+      <c r="R97" t="s">
+        <v>71</v>
+      </c>
+      <c r="S97" s="1">
+        <v>43770.04166666667</v>
+      </c>
+      <c r="T97" t="s">
+        <v>32</v>
+      </c>
+      <c r="U97" t="s">
+        <v>58</v>
+      </c>
+      <c r="V97" s="1">
+        <v>44063.04166666667</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>40006019</v>
+      </c>
+      <c r="B98" t="s">
+        <v>377</v>
+      </c>
+      <c r="C98" t="s">
+        <v>378</v>
+      </c>
+      <c r="D98" t="s">
+        <v>379</v>
+      </c>
+      <c r="E98" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" t="s">
+        <v>27</v>
+      </c>
+      <c r="H98" t="s">
+        <v>267</v>
+      </c>
+      <c r="I98" t="s">
+        <v>29</v>
+      </c>
+      <c r="J98" t="s">
+        <v>30</v>
+      </c>
+      <c r="K98" t="s">
+        <v>53</v>
+      </c>
+      <c r="L98" t="s">
+        <v>29</v>
+      </c>
+      <c r="M98" t="s">
+        <v>30</v>
+      </c>
+      <c r="N98" t="s">
+        <v>80</v>
+      </c>
+      <c r="O98" t="s">
+        <v>29</v>
+      </c>
+      <c r="P98" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>380</v>
+      </c>
+      <c r="R98" t="s">
+        <v>23</v>
+      </c>
+      <c r="S98" t="s">
+        <v>23</v>
+      </c>
+      <c r="T98" t="s">
+        <v>32</v>
+      </c>
+      <c r="U98" t="s">
+        <v>23</v>
+      </c>
+      <c r="V98" s="1">
+        <v>45813.04166666667</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>40002713</v>
+      </c>
+      <c r="B99" t="s">
+        <v>381</v>
+      </c>
+      <c r="C99" t="s">
+        <v>382</v>
+      </c>
+      <c r="D99" t="s">
+        <v>383</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" t="s">
+        <v>137</v>
+      </c>
+      <c r="I99" t="s">
+        <v>29</v>
+      </c>
+      <c r="J99" t="s">
+        <v>30</v>
+      </c>
+      <c r="K99">
+        <v>2030</v>
+      </c>
+      <c r="L99" t="s">
+        <v>29</v>
+      </c>
+      <c r="M99" t="s">
+        <v>30</v>
+      </c>
+      <c r="N99">
+        <v>2040</v>
+      </c>
+      <c r="O99" t="s">
+        <v>29</v>
+      </c>
+      <c r="P99">
+        <v>2040</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>384</v>
+      </c>
+      <c r="R99" t="s">
+        <v>71</v>
+      </c>
+      <c r="S99" s="1">
+        <v>43647.04166666667</v>
+      </c>
+      <c r="T99" t="s">
+        <v>32</v>
+      </c>
+      <c r="U99" t="s">
+        <v>23</v>
+      </c>
+      <c r="V99" s="1">
+        <v>45365.04166666667</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>40014384</v>
+      </c>
+      <c r="B100" t="s">
+        <v>385</v>
+      </c>
+      <c r="C100" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" t="s">
+        <v>36</v>
+      </c>
+      <c r="G100" t="s">
+        <v>37</v>
+      </c>
+      <c r="H100" t="s">
+        <v>38</v>
+      </c>
+      <c r="I100" t="s">
+        <v>29</v>
+      </c>
+      <c r="J100" t="s">
+        <v>30</v>
+      </c>
+      <c r="K100">
+        <v>2030</v>
+      </c>
+      <c r="L100" t="s">
+        <v>23</v>
+      </c>
+      <c r="M100" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" t="s">
+        <v>23</v>
+      </c>
+      <c r="O100" t="s">
+        <v>23</v>
+      </c>
+      <c r="P100" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>386</v>
+      </c>
+      <c r="R100" t="s">
+        <v>23</v>
+      </c>
+      <c r="S100" t="s">
+        <v>23</v>
+      </c>
+      <c r="T100" t="s">
+        <v>32</v>
+      </c>
+      <c r="U100" t="s">
+        <v>23</v>
+      </c>
+      <c r="V100" s="1">
+        <v>44805.04166666667</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>40003040</v>
+      </c>
+      <c r="B101" t="s">
+        <v>387</v>
+      </c>
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" t="s">
+        <v>285</v>
+      </c>
+      <c r="G101" t="s">
+        <v>134</v>
+      </c>
+      <c r="H101" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" t="s">
+        <v>29</v>
+      </c>
+      <c r="J101" t="s">
+        <v>30</v>
+      </c>
+      <c r="K101">
+        <v>2030</v>
+      </c>
+      <c r="L101" t="s">
+        <v>29</v>
+      </c>
+      <c r="M101" t="s">
+        <v>30</v>
+      </c>
+      <c r="N101">
+        <v>2045</v>
+      </c>
+      <c r="O101" t="s">
+        <v>29</v>
+      </c>
+      <c r="P101">
+        <v>2045</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>388</v>
+      </c>
+      <c r="R101" t="s">
+        <v>71</v>
+      </c>
+      <c r="S101" s="1">
+        <v>44952.04166666667</v>
+      </c>
+      <c r="T101" t="s">
+        <v>32</v>
+      </c>
+      <c r="U101" t="s">
+        <v>23</v>
+      </c>
+      <c r="V101" s="1">
+        <v>45596.04166666667</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>40000755</v>
+      </c>
+      <c r="B102" t="s">
+        <v>389</v>
+      </c>
+      <c r="C102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" t="s">
+        <v>390</v>
+      </c>
+      <c r="E102" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" t="s">
+        <v>70</v>
+      </c>
+      <c r="G102" t="s">
+        <v>66</v>
+      </c>
+      <c r="H102" t="s">
+        <v>363</v>
+      </c>
+      <c r="I102" t="s">
+        <v>29</v>
+      </c>
+      <c r="J102" t="s">
+        <v>30</v>
+      </c>
+      <c r="K102" t="s">
+        <v>53</v>
+      </c>
+      <c r="L102" t="s">
+        <v>23</v>
+      </c>
+      <c r="M102" t="s">
+        <v>23</v>
+      </c>
+      <c r="N102" t="s">
+        <v>23</v>
+      </c>
+      <c r="O102" t="s">
+        <v>23</v>
+      </c>
+      <c r="P102" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>391</v>
+      </c>
+      <c r="R102" t="s">
+        <v>71</v>
+      </c>
+      <c r="S102" s="1">
+        <v>44286.04166666667</v>
+      </c>
+      <c r="T102" t="s">
+        <v>32</v>
+      </c>
+      <c r="U102" t="s">
+        <v>23</v>
+      </c>
+      <c r="V102" s="1">
+        <v>44791.04166666667</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>40002060</v>
+      </c>
+      <c r="B103" t="s">
+        <v>392</v>
+      </c>
+      <c r="C103" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" t="s">
+        <v>393</v>
+      </c>
+      <c r="G103" t="s">
+        <v>51</v>
+      </c>
+      <c r="H103" t="s">
+        <v>67</v>
+      </c>
+      <c r="I103" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" t="s">
+        <v>30</v>
+      </c>
+      <c r="K103">
+        <v>2034</v>
+      </c>
+      <c r="L103" t="s">
+        <v>23</v>
+      </c>
+      <c r="M103" t="s">
+        <v>23</v>
+      </c>
+      <c r="N103" t="s">
+        <v>23</v>
+      </c>
+      <c r="O103" t="s">
+        <v>23</v>
+      </c>
+      <c r="P103" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>394</v>
+      </c>
+      <c r="R103" t="s">
+        <v>71</v>
+      </c>
+      <c r="S103" s="1">
+        <v>44020.04166666667</v>
+      </c>
+      <c r="T103" t="s">
+        <v>32</v>
+      </c>
+      <c r="U103" t="s">
+        <v>23</v>
+      </c>
+      <c r="V103" s="1">
+        <v>45834.04166666667</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>40000926</v>
+      </c>
+      <c r="B104" t="s">
+        <v>395</v>
+      </c>
+      <c r="C104" t="s">
+        <v>396</v>
+      </c>
+      <c r="D104" t="s">
+        <v>397</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>98</v>
+      </c>
+      <c r="G104" t="s">
+        <v>27</v>
+      </c>
+      <c r="H104" t="s">
+        <v>146</v>
+      </c>
+      <c r="I104" t="s">
+        <v>29</v>
+      </c>
+      <c r="J104" t="s">
+        <v>30</v>
+      </c>
+      <c r="K104">
+        <v>2030</v>
+      </c>
+      <c r="L104" t="s">
+        <v>29</v>
+      </c>
+      <c r="M104" t="s">
+        <v>30</v>
+      </c>
+      <c r="N104">
+        <v>2035</v>
+      </c>
+      <c r="O104" t="s">
+        <v>29</v>
+      </c>
+      <c r="P104">
+        <v>2035</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>398</v>
+      </c>
+      <c r="R104" t="s">
+        <v>71</v>
+      </c>
+      <c r="S104" s="1">
+        <v>44013.04166666667</v>
+      </c>
+      <c r="T104" t="s">
+        <v>32</v>
+      </c>
+      <c r="U104" t="s">
+        <v>23</v>
+      </c>
+      <c r="V104" s="1">
+        <v>45330.04166666667</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>40017347</v>
+      </c>
+      <c r="B105" t="s">
+        <v>399</v>
+      </c>
+      <c r="C105" t="s">
+        <v>23</v>
+      </c>
+      <c r="D105" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105" t="s">
+        <v>49</v>
+      </c>
+      <c r="F105" t="s">
+        <v>70</v>
+      </c>
+      <c r="G105" t="s">
+        <v>66</v>
+      </c>
+      <c r="H105" t="s">
+        <v>38</v>
+      </c>
+      <c r="I105" t="s">
+        <v>29</v>
+      </c>
+      <c r="J105" t="s">
+        <v>30</v>
+      </c>
+      <c r="K105">
+        <v>2030</v>
+      </c>
+      <c r="L105" t="s">
+        <v>23</v>
+      </c>
+      <c r="M105" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" t="s">
+        <v>23</v>
+      </c>
+      <c r="O105" t="s">
+        <v>23</v>
+      </c>
+      <c r="P105" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>400</v>
+      </c>
+      <c r="R105" t="s">
+        <v>23</v>
+      </c>
+      <c r="S105" t="s">
+        <v>23</v>
+      </c>
+      <c r="T105" t="s">
+        <v>32</v>
+      </c>
+      <c r="U105" t="s">
+        <v>23</v>
+      </c>
+      <c r="V105" s="1">
+        <v>45876.04166666667</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>40009523</v>
+      </c>
+      <c r="B106" t="s">
+        <v>401</v>
+      </c>
+      <c r="C106" t="s">
+        <v>402</v>
+      </c>
+      <c r="D106" t="s">
+        <v>403</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>280</v>
+      </c>
+      <c r="G106" t="s">
+        <v>66</v>
+      </c>
+      <c r="H106" t="s">
+        <v>146</v>
+      </c>
+      <c r="I106" t="s">
+        <v>29</v>
+      </c>
+      <c r="J106" t="s">
+        <v>30</v>
+      </c>
+      <c r="K106">
+        <v>2030</v>
+      </c>
+      <c r="L106" t="s">
+        <v>29</v>
+      </c>
+      <c r="M106" t="s">
+        <v>30</v>
+      </c>
+      <c r="N106">
+        <v>2045</v>
+      </c>
+      <c r="O106" t="s">
+        <v>29</v>
+      </c>
+      <c r="P106">
+        <v>2045</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>404</v>
+      </c>
+      <c r="R106" t="s">
+        <v>23</v>
+      </c>
+      <c r="S106" t="s">
+        <v>23</v>
+      </c>
+      <c r="T106" t="s">
+        <v>32</v>
+      </c>
+      <c r="U106" t="s">
+        <v>23</v>
+      </c>
+      <c r="V106" s="1">
+        <v>45939.04166666667</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>40016063</v>
+      </c>
+      <c r="B107" t="s">
+        <v>405</v>
+      </c>
+      <c r="C107" t="s">
+        <v>406</v>
+      </c>
+      <c r="D107" t="s">
+        <v>407</v>
+      </c>
+      <c r="E107" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" t="s">
+        <v>160</v>
+      </c>
+      <c r="G107" t="s">
+        <v>66</v>
+      </c>
+      <c r="H107" t="s">
+        <v>146</v>
+      </c>
+      <c r="I107" t="s">
+        <v>29</v>
+      </c>
+      <c r="J107" t="s">
+        <v>30</v>
+      </c>
+      <c r="K107">
+        <v>2030</v>
+      </c>
+      <c r="L107" t="s">
+        <v>29</v>
+      </c>
+      <c r="M107" t="s">
+        <v>30</v>
+      </c>
+      <c r="N107">
+        <v>2040</v>
+      </c>
+      <c r="O107" t="s">
+        <v>29</v>
+      </c>
+      <c r="P107">
+        <v>2040</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>408</v>
+      </c>
+      <c r="R107" t="s">
+        <v>71</v>
+      </c>
+      <c r="S107" s="1">
+        <v>43647.04166666667</v>
+      </c>
+      <c r="T107" t="s">
+        <v>32</v>
+      </c>
+      <c r="U107" t="s">
+        <v>23</v>
+      </c>
+      <c r="V107" s="1">
+        <v>46212.04166666667</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>40010168</v>
+      </c>
+      <c r="B108" t="s">
+        <v>409</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108" t="s">
+        <v>49</v>
+      </c>
+      <c r="F108" t="s">
+        <v>50</v>
+      </c>
+      <c r="G108" t="s">
+        <v>51</v>
+      </c>
+      <c r="H108" t="s">
+        <v>410</v>
+      </c>
+      <c r="I108" t="s">
+        <v>29</v>
+      </c>
+      <c r="J108" t="s">
+        <v>125</v>
+      </c>
+      <c r="K108">
+        <v>2030</v>
+      </c>
+      <c r="L108" t="s">
+        <v>23</v>
+      </c>
+      <c r="M108" t="s">
+        <v>23</v>
+      </c>
+      <c r="N108" t="s">
+        <v>23</v>
+      </c>
+      <c r="O108" t="s">
+        <v>23</v>
+      </c>
+      <c r="P108" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>411</v>
+      </c>
+      <c r="R108" t="s">
+        <v>23</v>
+      </c>
+      <c r="S108" t="s">
+        <v>23</v>
+      </c>
+      <c r="T108" t="s">
+        <v>127</v>
+      </c>
+      <c r="U108" t="s">
+        <v>23</v>
+      </c>
+      <c r="V108" s="1">
+        <v>44562.04166666667</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>40025334</v>
+      </c>
+      <c r="B109" t="s">
+        <v>412</v>
+      </c>
+      <c r="C109" t="s">
+        <v>413</v>
+      </c>
+      <c r="D109" t="s">
+        <v>414</v>
+      </c>
+      <c r="E109" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" t="s">
+        <v>50</v>
+      </c>
+      <c r="G109" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" t="s">
+        <v>247</v>
+      </c>
+      <c r="I109" t="s">
+        <v>29</v>
+      </c>
+      <c r="J109" t="s">
+        <v>30</v>
+      </c>
+      <c r="K109" t="s">
+        <v>53</v>
+      </c>
+      <c r="L109" t="s">
+        <v>23</v>
+      </c>
+      <c r="M109" t="s">
+        <v>23</v>
+      </c>
+      <c r="N109" t="s">
+        <v>23</v>
+      </c>
+      <c r="O109" t="s">
+        <v>23</v>
+      </c>
+      <c r="P109" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>415</v>
+      </c>
+      <c r="R109" t="s">
+        <v>23</v>
+      </c>
+      <c r="S109" t="s">
+        <v>23</v>
+      </c>
+      <c r="T109" t="s">
+        <v>32</v>
+      </c>
+      <c r="U109" t="s">
+        <v>23</v>
+      </c>
+      <c r="V109" s="1">
+        <v>46086.04166666667</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>40008764</v>
+      </c>
+      <c r="B110" t="s">
+        <v>416</v>
+      </c>
+      <c r="C110" t="s">
+        <v>417</v>
+      </c>
+      <c r="D110" t="s">
+        <v>418</v>
+      </c>
+      <c r="E110" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" t="s">
+        <v>70</v>
+      </c>
+      <c r="G110" t="s">
+        <v>66</v>
+      </c>
+      <c r="H110" t="s">
+        <v>165</v>
+      </c>
+      <c r="I110" t="s">
+        <v>29</v>
+      </c>
+      <c r="J110" t="s">
+        <v>30</v>
+      </c>
+      <c r="K110" t="s">
+        <v>53</v>
+      </c>
+      <c r="L110" t="s">
+        <v>23</v>
+      </c>
+      <c r="M110" t="s">
+        <v>23</v>
+      </c>
+      <c r="N110" t="s">
+        <v>23</v>
+      </c>
+      <c r="O110" t="s">
+        <v>39</v>
+      </c>
+      <c r="P110" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>419</v>
+      </c>
+      <c r="R110" t="s">
+        <v>71</v>
+      </c>
+      <c r="S110" s="1">
+        <v>43647.04166666667</v>
+      </c>
+      <c r="T110" t="s">
+        <v>32</v>
+      </c>
+      <c r="U110" t="s">
+        <v>58</v>
+      </c>
+      <c r="V110" s="1">
+        <v>45407.04166666667</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>40009186</v>
+      </c>
+      <c r="B111" t="s">
+        <v>420</v>
+      </c>
+      <c r="C111" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" t="s">
+        <v>49</v>
+      </c>
+      <c r="F111" t="s">
+        <v>218</v>
+      </c>
+      <c r="G111" t="s">
+        <v>219</v>
+      </c>
+      <c r="H111" t="s">
+        <v>340</v>
+      </c>
+      <c r="I111" t="s">
+        <v>29</v>
+      </c>
+      <c r="J111" t="s">
+        <v>30</v>
+      </c>
+      <c r="K111">
+        <v>2030</v>
+      </c>
+      <c r="L111" t="s">
+        <v>23</v>
+      </c>
+      <c r="M111" t="s">
+        <v>23</v>
+      </c>
+      <c r="N111" t="s">
+        <v>23</v>
+      </c>
+      <c r="O111" t="s">
+        <v>23</v>
+      </c>
+      <c r="P111" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>421</v>
+      </c>
+      <c r="R111" t="s">
+        <v>23</v>
+      </c>
+      <c r="S111" t="s">
+        <v>23</v>
+      </c>
+      <c r="T111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U111" t="s">
+        <v>23</v>
+      </c>
+      <c r="V111" s="1">
+        <v>45134.04166666667</v>
       </c>
     </row>
   </sheetData>
